--- a/scripts/TEMPLATE_MAIN.xlsx
+++ b/scripts/TEMPLATE_MAIN.xlsx
@@ -555,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -743,6 +743,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2622,67 +2625,67 @@
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="B7" s="14" t="n"/>
-      <c r="D7" s="15" t="n"/>
+      <c r="D7" s="42" t="n"/>
       <c r="K7" s="16" t="n"/>
       <c r="L7" s="14" t="n"/>
-      <c r="N7" s="15" t="n"/>
+      <c r="N7" s="42" t="n"/>
       <c r="U7" s="16" t="n"/>
       <c r="V7" s="14" t="n"/>
-      <c r="X7" s="15" t="n"/>
+      <c r="X7" s="42" t="n"/>
       <c r="AE7" s="16" t="n"/>
       <c r="AF7" s="14" t="n"/>
-      <c r="AH7" s="15" t="n"/>
+      <c r="AH7" s="42" t="n"/>
       <c r="AO7" s="16" t="n"/>
       <c r="AP7" s="14" t="n"/>
-      <c r="AR7" s="15" t="n"/>
+      <c r="AR7" s="42" t="n"/>
       <c r="AY7" s="16" t="n"/>
       <c r="AZ7" s="14" t="n"/>
-      <c r="BB7" s="15" t="n"/>
+      <c r="BB7" s="42" t="n"/>
       <c r="BI7" s="16" t="n"/>
       <c r="BJ7" s="14" t="n"/>
-      <c r="BL7" s="15" t="n"/>
+      <c r="BL7" s="42" t="n"/>
       <c r="BS7" s="16" t="n"/>
       <c r="BT7" s="14" t="n"/>
-      <c r="BV7" s="15" t="n"/>
+      <c r="BV7" s="42" t="n"/>
       <c r="CC7" s="16" t="n"/>
       <c r="CD7" s="14" t="n"/>
-      <c r="CF7" s="15" t="n"/>
+      <c r="CF7" s="42" t="n"/>
       <c r="CM7" s="16" t="n"/>
       <c r="CN7" s="14" t="n"/>
-      <c r="CP7" s="15" t="n"/>
+      <c r="CP7" s="42" t="n"/>
       <c r="CW7" s="16" t="n"/>
       <c r="CX7" s="14" t="n"/>
-      <c r="CZ7" s="15" t="n"/>
+      <c r="CZ7" s="42" t="n"/>
       <c r="DG7" s="16" t="n"/>
       <c r="DH7" s="14" t="n"/>
-      <c r="DJ7" s="15" t="n"/>
+      <c r="DJ7" s="42" t="n"/>
       <c r="DQ7" s="16" t="n"/>
       <c r="DR7" s="14" t="n"/>
-      <c r="DT7" s="15" t="n"/>
+      <c r="DT7" s="42" t="n"/>
       <c r="EA7" s="16" t="n"/>
       <c r="EB7" s="14" t="n"/>
-      <c r="ED7" s="15" t="n"/>
+      <c r="ED7" s="42" t="n"/>
       <c r="EK7" s="16" t="n"/>
       <c r="EL7" s="14" t="n"/>
-      <c r="EN7" s="15" t="n"/>
+      <c r="EN7" s="42" t="n"/>
       <c r="EU7" s="16" t="n"/>
       <c r="EV7" s="14" t="n"/>
-      <c r="EX7" s="15" t="n"/>
+      <c r="EX7" s="42" t="n"/>
       <c r="FE7" s="16" t="n"/>
       <c r="FF7" s="14" t="n"/>
-      <c r="FH7" s="15" t="n"/>
+      <c r="FH7" s="42" t="n"/>
       <c r="FO7" s="16" t="n"/>
       <c r="FP7" s="14" t="n"/>
-      <c r="FR7" s="15" t="n"/>
+      <c r="FR7" s="42" t="n"/>
       <c r="FY7" s="16" t="n"/>
       <c r="FZ7" s="14" t="n"/>
-      <c r="GB7" s="15" t="n"/>
+      <c r="GB7" s="42" t="n"/>
       <c r="GI7" s="16" t="n"/>
       <c r="GJ7" s="14" t="n"/>
-      <c r="GL7" s="15" t="n"/>
+      <c r="GL7" s="42" t="n"/>
       <c r="GS7" s="16" t="n"/>
       <c r="GT7" s="14" t="n"/>
-      <c r="GV7" s="15" t="n"/>
+      <c r="GV7" s="42" t="n"/>
       <c r="HC7" s="16" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
@@ -2691,147 +2694,147 @@
           <t>ページ</t>
         </is>
       </c>
-      <c r="F8" s="18" t="n"/>
+      <c r="F8" s="43" t="n"/>
       <c r="K8" s="16" t="n"/>
       <c r="N8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="P8" s="18" t="n"/>
+      <c r="P8" s="43" t="n"/>
       <c r="U8" s="16" t="n"/>
       <c r="X8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="Z8" s="18" t="n"/>
+      <c r="Z8" s="43" t="n"/>
       <c r="AE8" s="16" t="n"/>
       <c r="AH8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="AJ8" s="18" t="n"/>
+      <c r="AJ8" s="43" t="n"/>
       <c r="AO8" s="16" t="n"/>
       <c r="AR8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="AT8" s="18" t="n"/>
+      <c r="AT8" s="43" t="n"/>
       <c r="AY8" s="16" t="n"/>
       <c r="BB8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BD8" s="18" t="n"/>
+      <c r="BD8" s="43" t="n"/>
       <c r="BI8" s="16" t="n"/>
       <c r="BL8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BN8" s="18" t="n"/>
+      <c r="BN8" s="43" t="n"/>
       <c r="BS8" s="16" t="n"/>
       <c r="BV8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BX8" s="18" t="n"/>
+      <c r="BX8" s="43" t="n"/>
       <c r="CC8" s="16" t="n"/>
       <c r="CF8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="CH8" s="18" t="n"/>
+      <c r="CH8" s="43" t="n"/>
       <c r="CM8" s="16" t="n"/>
       <c r="CP8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="CR8" s="18" t="n"/>
+      <c r="CR8" s="43" t="n"/>
       <c r="CW8" s="16" t="n"/>
       <c r="CZ8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DB8" s="18" t="n"/>
+      <c r="DB8" s="43" t="n"/>
       <c r="DG8" s="16" t="n"/>
       <c r="DJ8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DL8" s="18" t="n"/>
+      <c r="DL8" s="43" t="n"/>
       <c r="DQ8" s="16" t="n"/>
       <c r="DT8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DV8" s="18" t="n"/>
+      <c r="DV8" s="43" t="n"/>
       <c r="EA8" s="16" t="n"/>
       <c r="ED8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EF8" s="18" t="n"/>
+      <c r="EF8" s="43" t="n"/>
       <c r="EK8" s="16" t="n"/>
       <c r="EN8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EP8" s="18" t="n"/>
+      <c r="EP8" s="43" t="n"/>
       <c r="EU8" s="16" t="n"/>
       <c r="EX8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EZ8" s="18" t="n"/>
+      <c r="EZ8" s="43" t="n"/>
       <c r="FE8" s="16" t="n"/>
       <c r="FH8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="FJ8" s="18" t="n"/>
+      <c r="FJ8" s="43" t="n"/>
       <c r="FO8" s="16" t="n"/>
       <c r="FR8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="FT8" s="18" t="n"/>
+      <c r="FT8" s="43" t="n"/>
       <c r="FY8" s="16" t="n"/>
       <c r="GB8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GD8" s="18" t="n"/>
+      <c r="GD8" s="43" t="n"/>
       <c r="GI8" s="16" t="n"/>
       <c r="GL8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GN8" s="18" t="n"/>
+      <c r="GN8" s="43" t="n"/>
       <c r="GS8" s="16" t="n"/>
       <c r="GV8" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GX8" s="18" t="n"/>
+      <c r="GX8" s="43" t="n"/>
       <c r="HC8" s="16" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
@@ -2845,7 +2848,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n"/>
+      <c r="E9" s="44" t="n"/>
       <c r="L9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2856,7 +2859,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="O9" s="20" t="n"/>
+      <c r="O9" s="44" t="n"/>
       <c r="V9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2867,7 +2870,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="Y9" s="20" t="n"/>
+      <c r="Y9" s="44" t="n"/>
       <c r="AF9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2878,7 +2881,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="AI9" s="20" t="n"/>
+      <c r="AI9" s="44" t="n"/>
       <c r="AP9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2889,7 +2892,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="AS9" s="20" t="n"/>
+      <c r="AS9" s="44" t="n"/>
       <c r="AZ9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2900,7 +2903,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BC9" s="20" t="n"/>
+      <c r="BC9" s="44" t="n"/>
       <c r="BJ9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2911,7 +2914,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BM9" s="20" t="n"/>
+      <c r="BM9" s="44" t="n"/>
       <c r="BT9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2922,7 +2925,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BW9" s="20" t="n"/>
+      <c r="BW9" s="44" t="n"/>
       <c r="CD9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2933,7 +2936,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="CG9" s="20" t="n"/>
+      <c r="CG9" s="44" t="n"/>
       <c r="CN9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2944,7 +2947,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="CQ9" s="20" t="n"/>
+      <c r="CQ9" s="44" t="n"/>
       <c r="CX9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2955,7 +2958,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DA9" s="20" t="n"/>
+      <c r="DA9" s="44" t="n"/>
       <c r="DH9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2966,7 +2969,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DK9" s="20" t="n"/>
+      <c r="DK9" s="44" t="n"/>
       <c r="DR9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2977,7 +2980,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DU9" s="20" t="n"/>
+      <c r="DU9" s="44" t="n"/>
       <c r="EB9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2988,7 +2991,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EE9" s="20" t="n"/>
+      <c r="EE9" s="44" t="n"/>
       <c r="EL9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -2999,7 +3002,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EO9" s="20" t="n"/>
+      <c r="EO9" s="44" t="n"/>
       <c r="EV9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -3010,7 +3013,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EY9" s="20" t="n"/>
+      <c r="EY9" s="44" t="n"/>
       <c r="FF9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -3021,7 +3024,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="FI9" s="20" t="n"/>
+      <c r="FI9" s="44" t="n"/>
       <c r="FP9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -3032,7 +3035,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="FS9" s="20" t="n"/>
+      <c r="FS9" s="44" t="n"/>
       <c r="FZ9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -3043,7 +3046,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GC9" s="20" t="n"/>
+      <c r="GC9" s="44" t="n"/>
       <c r="GJ9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -3054,7 +3057,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GM9" s="20" t="n"/>
+      <c r="GM9" s="44" t="n"/>
       <c r="GT9" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -3065,7 +3068,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GW9" s="20" t="n"/>
+      <c r="GW9" s="44" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="B10" s="21" t="n"/>
@@ -3074,147 +3077,147 @@
           <t>月</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n"/>
+      <c r="E10" s="45" t="n"/>
       <c r="L10" s="21" t="n"/>
       <c r="M10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="O10" s="23" t="n"/>
+      <c r="O10" s="45" t="n"/>
       <c r="V10" s="21" t="n"/>
       <c r="W10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="Y10" s="23" t="n"/>
+      <c r="Y10" s="45" t="n"/>
       <c r="AF10" s="21" t="n"/>
       <c r="AG10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AI10" s="23" t="n"/>
+      <c r="AI10" s="45" t="n"/>
       <c r="AP10" s="21" t="n"/>
       <c r="AQ10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AS10" s="23" t="n"/>
+      <c r="AS10" s="45" t="n"/>
       <c r="AZ10" s="21" t="n"/>
       <c r="BA10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BC10" s="23" t="n"/>
+      <c r="BC10" s="45" t="n"/>
       <c r="BJ10" s="21" t="n"/>
       <c r="BK10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BM10" s="23" t="n"/>
+      <c r="BM10" s="45" t="n"/>
       <c r="BT10" s="21" t="n"/>
       <c r="BU10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BW10" s="23" t="n"/>
+      <c r="BW10" s="45" t="n"/>
       <c r="CD10" s="21" t="n"/>
       <c r="CE10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="CG10" s="23" t="n"/>
+      <c r="CG10" s="45" t="n"/>
       <c r="CN10" s="21" t="n"/>
       <c r="CO10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="CQ10" s="23" t="n"/>
+      <c r="CQ10" s="45" t="n"/>
       <c r="CX10" s="21" t="n"/>
       <c r="CY10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DA10" s="23" t="n"/>
+      <c r="DA10" s="45" t="n"/>
       <c r="DH10" s="21" t="n"/>
       <c r="DI10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DK10" s="23" t="n"/>
+      <c r="DK10" s="45" t="n"/>
       <c r="DR10" s="21" t="n"/>
       <c r="DS10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DU10" s="23" t="n"/>
+      <c r="DU10" s="45" t="n"/>
       <c r="EB10" s="21" t="n"/>
       <c r="EC10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EE10" s="23" t="n"/>
+      <c r="EE10" s="45" t="n"/>
       <c r="EL10" s="21" t="n"/>
       <c r="EM10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EO10" s="23" t="n"/>
+      <c r="EO10" s="45" t="n"/>
       <c r="EV10" s="21" t="n"/>
       <c r="EW10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EY10" s="23" t="n"/>
+      <c r="EY10" s="45" t="n"/>
       <c r="FF10" s="21" t="n"/>
       <c r="FG10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="FI10" s="23" t="n"/>
+      <c r="FI10" s="45" t="n"/>
       <c r="FP10" s="21" t="n"/>
       <c r="FQ10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="FS10" s="23" t="n"/>
+      <c r="FS10" s="45" t="n"/>
       <c r="FZ10" s="21" t="n"/>
       <c r="GA10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GC10" s="23" t="n"/>
+      <c r="GC10" s="45" t="n"/>
       <c r="GJ10" s="21" t="n"/>
       <c r="GK10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GM10" s="23" t="n"/>
+      <c r="GM10" s="45" t="n"/>
       <c r="GT10" s="21" t="n"/>
       <c r="GU10" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GW10" s="23" t="n"/>
+      <c r="GW10" s="45" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="B11" s="21" t="n"/>
@@ -3228,7 +3231,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n"/>
+      <c r="E11" s="46" t="n"/>
       <c r="L11" s="21" t="n"/>
       <c r="M11" s="22" t="inlineStr">
         <is>
@@ -3240,7 +3243,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="O11" s="24" t="n"/>
+      <c r="O11" s="46" t="n"/>
       <c r="V11" s="21" t="n"/>
       <c r="W11" s="22" t="inlineStr">
         <is>
@@ -3252,7 +3255,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="Y11" s="24" t="n"/>
+      <c r="Y11" s="46" t="n"/>
       <c r="AF11" s="21" t="n"/>
       <c r="AG11" s="22" t="inlineStr">
         <is>
@@ -3264,7 +3267,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="AI11" s="24" t="n"/>
+      <c r="AI11" s="46" t="n"/>
       <c r="AP11" s="21" t="n"/>
       <c r="AQ11" s="22" t="inlineStr">
         <is>
@@ -3276,7 +3279,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="AS11" s="24" t="n"/>
+      <c r="AS11" s="46" t="n"/>
       <c r="AZ11" s="21" t="n"/>
       <c r="BA11" s="22" t="inlineStr">
         <is>
@@ -3288,7 +3291,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BC11" s="24" t="n"/>
+      <c r="BC11" s="46" t="n"/>
       <c r="BJ11" s="21" t="n"/>
       <c r="BK11" s="22" t="inlineStr">
         <is>
@@ -3300,7 +3303,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BM11" s="24" t="n"/>
+      <c r="BM11" s="46" t="n"/>
       <c r="BT11" s="21" t="n"/>
       <c r="BU11" s="22" t="inlineStr">
         <is>
@@ -3312,7 +3315,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BW11" s="24" t="n"/>
+      <c r="BW11" s="46" t="n"/>
       <c r="CD11" s="21" t="n"/>
       <c r="CE11" s="22" t="inlineStr">
         <is>
@@ -3324,7 +3327,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="CG11" s="24" t="n"/>
+      <c r="CG11" s="46" t="n"/>
       <c r="CN11" s="21" t="n"/>
       <c r="CO11" s="22" t="inlineStr">
         <is>
@@ -3336,7 +3339,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="CQ11" s="24" t="n"/>
+      <c r="CQ11" s="46" t="n"/>
       <c r="CX11" s="21" t="n"/>
       <c r="CY11" s="22" t="inlineStr">
         <is>
@@ -3348,7 +3351,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DA11" s="24" t="n"/>
+      <c r="DA11" s="46" t="n"/>
       <c r="DH11" s="21" t="n"/>
       <c r="DI11" s="22" t="inlineStr">
         <is>
@@ -3360,7 +3363,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DK11" s="24" t="n"/>
+      <c r="DK11" s="46" t="n"/>
       <c r="DR11" s="21" t="n"/>
       <c r="DS11" s="22" t="inlineStr">
         <is>
@@ -3372,7 +3375,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DU11" s="24" t="n"/>
+      <c r="DU11" s="46" t="n"/>
       <c r="EB11" s="21" t="n"/>
       <c r="EC11" s="22" t="inlineStr">
         <is>
@@ -3384,7 +3387,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EE11" s="24" t="n"/>
+      <c r="EE11" s="46" t="n"/>
       <c r="EL11" s="21" t="n"/>
       <c r="EM11" s="22" t="inlineStr">
         <is>
@@ -3396,7 +3399,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EO11" s="24" t="n"/>
+      <c r="EO11" s="46" t="n"/>
       <c r="EV11" s="21" t="n"/>
       <c r="EW11" s="22" t="inlineStr">
         <is>
@@ -3408,7 +3411,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EY11" s="24" t="n"/>
+      <c r="EY11" s="46" t="n"/>
       <c r="FF11" s="21" t="n"/>
       <c r="FG11" s="22" t="inlineStr">
         <is>
@@ -3420,7 +3423,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="FI11" s="24" t="n"/>
+      <c r="FI11" s="46" t="n"/>
       <c r="FP11" s="21" t="n"/>
       <c r="FQ11" s="22" t="inlineStr">
         <is>
@@ -3432,7 +3435,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="FS11" s="24" t="n"/>
+      <c r="FS11" s="46" t="n"/>
       <c r="FZ11" s="21" t="n"/>
       <c r="GA11" s="22" t="inlineStr">
         <is>
@@ -3444,7 +3447,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GC11" s="24" t="n"/>
+      <c r="GC11" s="46" t="n"/>
       <c r="GJ11" s="21" t="n"/>
       <c r="GK11" s="22" t="inlineStr">
         <is>
@@ -3456,7 +3459,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GM11" s="24" t="n"/>
+      <c r="GM11" s="46" t="n"/>
       <c r="GT11" s="21" t="n"/>
       <c r="GU11" s="22" t="inlineStr">
         <is>
@@ -3468,7 +3471,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GW11" s="24" t="n"/>
+      <c r="GW11" s="46" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="B12" s="25" t="n"/>
@@ -3837,132 +3840,132 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="30" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="D17" s="31" t="n"/>
-      <c r="L17" s="30" t="inlineStr">
+      <c r="D17" s="48" t="n"/>
+      <c r="L17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="N17" s="31" t="n"/>
-      <c r="V17" s="30" t="inlineStr">
+      <c r="N17" s="48" t="n"/>
+      <c r="V17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="X17" s="31" t="n"/>
-      <c r="AF17" s="30" t="inlineStr">
+      <c r="X17" s="48" t="n"/>
+      <c r="AF17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="AH17" s="31" t="n"/>
-      <c r="AP17" s="30" t="inlineStr">
+      <c r="AH17" s="48" t="n"/>
+      <c r="AP17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="AR17" s="31" t="n"/>
-      <c r="AZ17" s="30" t="inlineStr">
+      <c r="AR17" s="48" t="n"/>
+      <c r="AZ17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BB17" s="31" t="n"/>
-      <c r="BJ17" s="30" t="inlineStr">
+      <c r="BB17" s="48" t="n"/>
+      <c r="BJ17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BL17" s="31" t="n"/>
-      <c r="BT17" s="30" t="inlineStr">
+      <c r="BL17" s="48" t="n"/>
+      <c r="BT17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BV17" s="31" t="n"/>
-      <c r="CD17" s="30" t="inlineStr">
+      <c r="BV17" s="48" t="n"/>
+      <c r="CD17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CF17" s="31" t="n"/>
-      <c r="CN17" s="30" t="inlineStr">
+      <c r="CF17" s="48" t="n"/>
+      <c r="CN17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CP17" s="31" t="n"/>
-      <c r="CX17" s="30" t="inlineStr">
+      <c r="CP17" s="48" t="n"/>
+      <c r="CX17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CZ17" s="31" t="n"/>
-      <c r="DH17" s="30" t="inlineStr">
+      <c r="CZ17" s="48" t="n"/>
+      <c r="DH17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="DJ17" s="31" t="n"/>
-      <c r="DR17" s="30" t="inlineStr">
+      <c r="DJ17" s="48" t="n"/>
+      <c r="DR17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="DT17" s="31" t="n"/>
-      <c r="EB17" s="30" t="inlineStr">
+      <c r="DT17" s="48" t="n"/>
+      <c r="EB17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="ED17" s="31" t="n"/>
-      <c r="EL17" s="30" t="inlineStr">
+      <c r="ED17" s="48" t="n"/>
+      <c r="EL17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="EN17" s="31" t="n"/>
-      <c r="EV17" s="30" t="inlineStr">
+      <c r="EN17" s="48" t="n"/>
+      <c r="EV17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="EX17" s="31" t="n"/>
-      <c r="FF17" s="30" t="inlineStr">
+      <c r="EX17" s="48" t="n"/>
+      <c r="FF17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="FH17" s="31" t="n"/>
-      <c r="FP17" s="30" t="inlineStr">
+      <c r="FH17" s="48" t="n"/>
+      <c r="FP17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="FR17" s="31" t="n"/>
-      <c r="FZ17" s="30" t="inlineStr">
+      <c r="FR17" s="48" t="n"/>
+      <c r="FZ17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GB17" s="31" t="n"/>
-      <c r="GJ17" s="30" t="inlineStr">
+      <c r="GB17" s="48" t="n"/>
+      <c r="GJ17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GL17" s="31" t="n"/>
-      <c r="GT17" s="30" t="inlineStr">
+      <c r="GL17" s="48" t="n"/>
+      <c r="GT17" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GV17" s="31" t="n"/>
+      <c r="GV17" s="48" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="B18" s="32" t="inlineStr">
@@ -3970,299 +3973,299 @@
           <t>欠席</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n"/>
+      <c r="C18" s="44" t="n"/>
       <c r="L18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="M18" s="20" t="n"/>
+      <c r="M18" s="44" t="n"/>
       <c r="V18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="W18" s="20" t="n"/>
+      <c r="W18" s="44" t="n"/>
       <c r="AF18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="AG18" s="20" t="n"/>
+      <c r="AG18" s="44" t="n"/>
       <c r="AP18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="AQ18" s="20" t="n"/>
+      <c r="AQ18" s="44" t="n"/>
       <c r="AZ18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BA18" s="20" t="n"/>
+      <c r="BA18" s="44" t="n"/>
       <c r="BJ18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BK18" s="20" t="n"/>
+      <c r="BK18" s="44" t="n"/>
       <c r="BT18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BU18" s="20" t="n"/>
+      <c r="BU18" s="44" t="n"/>
       <c r="CD18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CE18" s="20" t="n"/>
+      <c r="CE18" s="44" t="n"/>
       <c r="CN18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CO18" s="20" t="n"/>
+      <c r="CO18" s="44" t="n"/>
       <c r="CX18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CY18" s="20" t="n"/>
+      <c r="CY18" s="44" t="n"/>
       <c r="DH18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="DI18" s="20" t="n"/>
+      <c r="DI18" s="44" t="n"/>
       <c r="DR18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="DS18" s="20" t="n"/>
+      <c r="DS18" s="44" t="n"/>
       <c r="EB18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EC18" s="20" t="n"/>
+      <c r="EC18" s="44" t="n"/>
       <c r="EL18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EM18" s="20" t="n"/>
+      <c r="EM18" s="44" t="n"/>
       <c r="EV18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EW18" s="20" t="n"/>
+      <c r="EW18" s="44" t="n"/>
       <c r="FF18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="FG18" s="20" t="n"/>
+      <c r="FG18" s="44" t="n"/>
       <c r="FP18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="FQ18" s="20" t="n"/>
+      <c r="FQ18" s="44" t="n"/>
       <c r="FZ18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GA18" s="20" t="n"/>
+      <c r="GA18" s="44" t="n"/>
       <c r="GJ18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GK18" s="20" t="n"/>
+      <c r="GK18" s="44" t="n"/>
       <c r="GT18" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GU18" s="20" t="n"/>
+      <c r="GU18" s="44" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
-      <c r="C19" s="33" t="n"/>
-      <c r="M19" s="33" t="n"/>
-      <c r="W19" s="33" t="n"/>
-      <c r="AG19" s="33" t="n"/>
-      <c r="AQ19" s="33" t="n"/>
-      <c r="BA19" s="33" t="n"/>
-      <c r="BK19" s="33" t="n"/>
-      <c r="BU19" s="33" t="n"/>
-      <c r="CE19" s="33" t="n"/>
-      <c r="CO19" s="33" t="n"/>
-      <c r="CY19" s="33" t="n"/>
-      <c r="DI19" s="33" t="n"/>
-      <c r="DS19" s="33" t="n"/>
-      <c r="EC19" s="33" t="n"/>
-      <c r="EM19" s="33" t="n"/>
-      <c r="EW19" s="33" t="n"/>
-      <c r="FG19" s="33" t="n"/>
-      <c r="FQ19" s="33" t="n"/>
-      <c r="GA19" s="33" t="n"/>
-      <c r="GK19" s="33" t="n"/>
-      <c r="GU19" s="33" t="n"/>
+      <c r="C19" s="49" t="n"/>
+      <c r="M19" s="49" t="n"/>
+      <c r="W19" s="49" t="n"/>
+      <c r="AG19" s="49" t="n"/>
+      <c r="AQ19" s="49" t="n"/>
+      <c r="BA19" s="49" t="n"/>
+      <c r="BK19" s="49" t="n"/>
+      <c r="BU19" s="49" t="n"/>
+      <c r="CE19" s="49" t="n"/>
+      <c r="CO19" s="49" t="n"/>
+      <c r="CY19" s="49" t="n"/>
+      <c r="DI19" s="49" t="n"/>
+      <c r="DS19" s="49" t="n"/>
+      <c r="EC19" s="49" t="n"/>
+      <c r="EM19" s="49" t="n"/>
+      <c r="EW19" s="49" t="n"/>
+      <c r="FG19" s="49" t="n"/>
+      <c r="FQ19" s="49" t="n"/>
+      <c r="GA19" s="49" t="n"/>
+      <c r="GK19" s="49" t="n"/>
+      <c r="GU19" s="49" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="H20" s="35" t="n"/>
-      <c r="I20" s="36" t="n"/>
-      <c r="L20" s="34" t="inlineStr">
+      <c r="H20" s="51" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="L20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="R20" s="35" t="n"/>
-      <c r="S20" s="36" t="n"/>
-      <c r="V20" s="34" t="inlineStr">
+      <c r="R20" s="51" t="n"/>
+      <c r="S20" s="52" t="n"/>
+      <c r="V20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AB20" s="35" t="n"/>
-      <c r="AC20" s="36" t="n"/>
-      <c r="AF20" s="34" t="inlineStr">
+      <c r="AB20" s="51" t="n"/>
+      <c r="AC20" s="52" t="n"/>
+      <c r="AF20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AL20" s="35" t="n"/>
-      <c r="AM20" s="36" t="n"/>
-      <c r="AP20" s="34" t="inlineStr">
+      <c r="AL20" s="51" t="n"/>
+      <c r="AM20" s="52" t="n"/>
+      <c r="AP20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AV20" s="35" t="n"/>
-      <c r="AW20" s="36" t="n"/>
-      <c r="AZ20" s="34" t="inlineStr">
+      <c r="AV20" s="51" t="n"/>
+      <c r="AW20" s="52" t="n"/>
+      <c r="AZ20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BF20" s="35" t="n"/>
-      <c r="BG20" s="36" t="n"/>
-      <c r="BJ20" s="34" t="inlineStr">
+      <c r="BF20" s="51" t="n"/>
+      <c r="BG20" s="52" t="n"/>
+      <c r="BJ20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BP20" s="35" t="n"/>
-      <c r="BQ20" s="36" t="n"/>
-      <c r="BT20" s="34" t="inlineStr">
+      <c r="BP20" s="51" t="n"/>
+      <c r="BQ20" s="52" t="n"/>
+      <c r="BT20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BZ20" s="35" t="n"/>
-      <c r="CA20" s="36" t="n"/>
-      <c r="CD20" s="34" t="inlineStr">
+      <c r="BZ20" s="51" t="n"/>
+      <c r="CA20" s="52" t="n"/>
+      <c r="CD20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="CJ20" s="35" t="n"/>
-      <c r="CK20" s="36" t="n"/>
-      <c r="CN20" s="34" t="inlineStr">
+      <c r="CJ20" s="51" t="n"/>
+      <c r="CK20" s="52" t="n"/>
+      <c r="CN20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="CT20" s="35" t="n"/>
-      <c r="CU20" s="36" t="n"/>
-      <c r="CX20" s="34" t="inlineStr">
+      <c r="CT20" s="51" t="n"/>
+      <c r="CU20" s="52" t="n"/>
+      <c r="CX20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DD20" s="35" t="n"/>
-      <c r="DE20" s="36" t="n"/>
-      <c r="DH20" s="34" t="inlineStr">
+      <c r="DD20" s="51" t="n"/>
+      <c r="DE20" s="52" t="n"/>
+      <c r="DH20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DN20" s="35" t="n"/>
-      <c r="DO20" s="36" t="n"/>
-      <c r="DR20" s="34" t="inlineStr">
+      <c r="DN20" s="51" t="n"/>
+      <c r="DO20" s="52" t="n"/>
+      <c r="DR20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DX20" s="35" t="n"/>
-      <c r="DY20" s="36" t="n"/>
-      <c r="EB20" s="34" t="inlineStr">
+      <c r="DX20" s="51" t="n"/>
+      <c r="DY20" s="52" t="n"/>
+      <c r="EB20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="EH20" s="35" t="n"/>
-      <c r="EI20" s="36" t="n"/>
-      <c r="EL20" s="34" t="inlineStr">
+      <c r="EH20" s="51" t="n"/>
+      <c r="EI20" s="52" t="n"/>
+      <c r="EL20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="ER20" s="35" t="n"/>
-      <c r="ES20" s="36" t="n"/>
-      <c r="EV20" s="34" t="inlineStr">
+      <c r="ER20" s="51" t="n"/>
+      <c r="ES20" s="52" t="n"/>
+      <c r="EV20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FB20" s="35" t="n"/>
-      <c r="FC20" s="36" t="n"/>
-      <c r="FF20" s="34" t="inlineStr">
+      <c r="FB20" s="51" t="n"/>
+      <c r="FC20" s="52" t="n"/>
+      <c r="FF20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FL20" s="35" t="n"/>
-      <c r="FM20" s="36" t="n"/>
-      <c r="FP20" s="34" t="inlineStr">
+      <c r="FL20" s="51" t="n"/>
+      <c r="FM20" s="52" t="n"/>
+      <c r="FP20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FV20" s="35" t="n"/>
-      <c r="FW20" s="36" t="n"/>
-      <c r="FZ20" s="34" t="inlineStr">
+      <c r="FV20" s="51" t="n"/>
+      <c r="FW20" s="52" t="n"/>
+      <c r="FZ20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GF20" s="35" t="n"/>
-      <c r="GG20" s="36" t="n"/>
-      <c r="GJ20" s="34" t="inlineStr">
+      <c r="GF20" s="51" t="n"/>
+      <c r="GG20" s="52" t="n"/>
+      <c r="GJ20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GP20" s="35" t="n"/>
-      <c r="GQ20" s="36" t="n"/>
-      <c r="GT20" s="34" t="inlineStr">
+      <c r="GP20" s="51" t="n"/>
+      <c r="GQ20" s="52" t="n"/>
+      <c r="GT20" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GZ20" s="35" t="n"/>
-      <c r="HA20" s="36" t="n"/>
+      <c r="GZ20" s="51" t="n"/>
+      <c r="HA20" s="52" t="n"/>
     </row>
     <row r="21" ht="12" customHeight="1">
       <c r="B21" s="37" t="inlineStr">
@@ -4270,127 +4273,127 @@
           <t>備考</t>
         </is>
       </c>
-      <c r="C21" s="38" t="n"/>
+      <c r="C21" s="53" t="n"/>
       <c r="L21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="M21" s="38" t="n"/>
+      <c r="M21" s="53" t="n"/>
       <c r="V21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="W21" s="38" t="n"/>
+      <c r="W21" s="53" t="n"/>
       <c r="AF21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="AG21" s="38" t="n"/>
+      <c r="AG21" s="53" t="n"/>
       <c r="AP21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="AQ21" s="38" t="n"/>
+      <c r="AQ21" s="53" t="n"/>
       <c r="AZ21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BA21" s="38" t="n"/>
+      <c r="BA21" s="53" t="n"/>
       <c r="BJ21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BK21" s="38" t="n"/>
+      <c r="BK21" s="53" t="n"/>
       <c r="BT21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BU21" s="38" t="n"/>
+      <c r="BU21" s="53" t="n"/>
       <c r="CD21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CE21" s="38" t="n"/>
+      <c r="CE21" s="53" t="n"/>
       <c r="CN21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CO21" s="38" t="n"/>
+      <c r="CO21" s="53" t="n"/>
       <c r="CX21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CY21" s="38" t="n"/>
+      <c r="CY21" s="53" t="n"/>
       <c r="DH21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="DI21" s="38" t="n"/>
+      <c r="DI21" s="53" t="n"/>
       <c r="DR21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="DS21" s="38" t="n"/>
+      <c r="DS21" s="53" t="n"/>
       <c r="EB21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EC21" s="38" t="n"/>
+      <c r="EC21" s="53" t="n"/>
       <c r="EL21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EM21" s="38" t="n"/>
+      <c r="EM21" s="53" t="n"/>
       <c r="EV21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EW21" s="38" t="n"/>
+      <c r="EW21" s="53" t="n"/>
       <c r="FF21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="FG21" s="38" t="n"/>
+      <c r="FG21" s="53" t="n"/>
       <c r="FP21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="FQ21" s="38" t="n"/>
+      <c r="FQ21" s="53" t="n"/>
       <c r="FZ21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GA21" s="38" t="n"/>
+      <c r="GA21" s="53" t="n"/>
       <c r="GJ21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GK21" s="38" t="n"/>
+      <c r="GK21" s="53" t="n"/>
       <c r="GT21" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GU21" s="38" t="n"/>
+      <c r="GU21" s="53" t="n"/>
     </row>
     <row r="22" ht="12" customHeight="1"/>
     <row r="23" ht="12" customHeight="1"/>
@@ -4610,67 +4613,67 @@
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="B27" s="14" t="n"/>
-      <c r="D27" s="15" t="n"/>
+      <c r="D27" s="42" t="n"/>
       <c r="K27" s="16" t="n"/>
       <c r="L27" s="14" t="n"/>
-      <c r="N27" s="15" t="n"/>
+      <c r="N27" s="42" t="n"/>
       <c r="U27" s="16" t="n"/>
       <c r="V27" s="14" t="n"/>
-      <c r="X27" s="15" t="n"/>
+      <c r="X27" s="42" t="n"/>
       <c r="AE27" s="16" t="n"/>
       <c r="AF27" s="14" t="n"/>
-      <c r="AH27" s="15" t="n"/>
+      <c r="AH27" s="42" t="n"/>
       <c r="AO27" s="16" t="n"/>
       <c r="AP27" s="14" t="n"/>
-      <c r="AR27" s="15" t="n"/>
+      <c r="AR27" s="42" t="n"/>
       <c r="AY27" s="16" t="n"/>
       <c r="AZ27" s="14" t="n"/>
-      <c r="BB27" s="15" t="n"/>
+      <c r="BB27" s="42" t="n"/>
       <c r="BI27" s="16" t="n"/>
       <c r="BJ27" s="14" t="n"/>
-      <c r="BL27" s="15" t="n"/>
+      <c r="BL27" s="42" t="n"/>
       <c r="BS27" s="16" t="n"/>
       <c r="BT27" s="14" t="n"/>
-      <c r="BV27" s="15" t="n"/>
+      <c r="BV27" s="42" t="n"/>
       <c r="CC27" s="16" t="n"/>
       <c r="CD27" s="14" t="n"/>
-      <c r="CF27" s="15" t="n"/>
+      <c r="CF27" s="42" t="n"/>
       <c r="CM27" s="16" t="n"/>
       <c r="CN27" s="14" t="n"/>
-      <c r="CP27" s="15" t="n"/>
+      <c r="CP27" s="42" t="n"/>
       <c r="CW27" s="16" t="n"/>
       <c r="CX27" s="14" t="n"/>
-      <c r="CZ27" s="15" t="n"/>
+      <c r="CZ27" s="42" t="n"/>
       <c r="DG27" s="16" t="n"/>
       <c r="DH27" s="14" t="n"/>
-      <c r="DJ27" s="15" t="n"/>
+      <c r="DJ27" s="42" t="n"/>
       <c r="DQ27" s="16" t="n"/>
       <c r="DR27" s="14" t="n"/>
-      <c r="DT27" s="15" t="n"/>
+      <c r="DT27" s="42" t="n"/>
       <c r="EA27" s="16" t="n"/>
       <c r="EB27" s="14" t="n"/>
-      <c r="ED27" s="15" t="n"/>
+      <c r="ED27" s="42" t="n"/>
       <c r="EK27" s="16" t="n"/>
       <c r="EL27" s="14" t="n"/>
-      <c r="EN27" s="15" t="n"/>
+      <c r="EN27" s="42" t="n"/>
       <c r="EU27" s="16" t="n"/>
       <c r="EV27" s="14" t="n"/>
-      <c r="EX27" s="15" t="n"/>
+      <c r="EX27" s="42" t="n"/>
       <c r="FE27" s="16" t="n"/>
       <c r="FF27" s="14" t="n"/>
-      <c r="FH27" s="15" t="n"/>
+      <c r="FH27" s="42" t="n"/>
       <c r="FO27" s="16" t="n"/>
       <c r="FP27" s="14" t="n"/>
-      <c r="FR27" s="15" t="n"/>
+      <c r="FR27" s="42" t="n"/>
       <c r="FY27" s="16" t="n"/>
       <c r="FZ27" s="14" t="n"/>
-      <c r="GB27" s="15" t="n"/>
+      <c r="GB27" s="42" t="n"/>
       <c r="GI27" s="16" t="n"/>
       <c r="GJ27" s="14" t="n"/>
-      <c r="GL27" s="15" t="n"/>
+      <c r="GL27" s="42" t="n"/>
       <c r="GS27" s="16" t="n"/>
       <c r="GT27" s="14" t="n"/>
-      <c r="GV27" s="15" t="n"/>
+      <c r="GV27" s="42" t="n"/>
       <c r="HC27" s="16" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -4679,147 +4682,147 @@
           <t>ページ</t>
         </is>
       </c>
-      <c r="F28" s="18" t="n"/>
+      <c r="F28" s="43" t="n"/>
       <c r="K28" s="16" t="n"/>
       <c r="N28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="P28" s="18" t="n"/>
+      <c r="P28" s="43" t="n"/>
       <c r="U28" s="16" t="n"/>
       <c r="X28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="Z28" s="18" t="n"/>
+      <c r="Z28" s="43" t="n"/>
       <c r="AE28" s="16" t="n"/>
       <c r="AH28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="AJ28" s="18" t="n"/>
+      <c r="AJ28" s="43" t="n"/>
       <c r="AO28" s="16" t="n"/>
       <c r="AR28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="AT28" s="18" t="n"/>
+      <c r="AT28" s="43" t="n"/>
       <c r="AY28" s="16" t="n"/>
       <c r="BB28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BD28" s="18" t="n"/>
+      <c r="BD28" s="43" t="n"/>
       <c r="BI28" s="16" t="n"/>
       <c r="BL28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BN28" s="18" t="n"/>
+      <c r="BN28" s="43" t="n"/>
       <c r="BS28" s="16" t="n"/>
       <c r="BV28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BX28" s="18" t="n"/>
+      <c r="BX28" s="43" t="n"/>
       <c r="CC28" s="16" t="n"/>
       <c r="CF28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="CH28" s="18" t="n"/>
+      <c r="CH28" s="43" t="n"/>
       <c r="CM28" s="16" t="n"/>
       <c r="CP28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="CR28" s="18" t="n"/>
+      <c r="CR28" s="43" t="n"/>
       <c r="CW28" s="16" t="n"/>
       <c r="CZ28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DB28" s="18" t="n"/>
+      <c r="DB28" s="43" t="n"/>
       <c r="DG28" s="16" t="n"/>
       <c r="DJ28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DL28" s="18" t="n"/>
+      <c r="DL28" s="43" t="n"/>
       <c r="DQ28" s="16" t="n"/>
       <c r="DT28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DV28" s="18" t="n"/>
+      <c r="DV28" s="43" t="n"/>
       <c r="EA28" s="16" t="n"/>
       <c r="ED28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EF28" s="18" t="n"/>
+      <c r="EF28" s="43" t="n"/>
       <c r="EK28" s="16" t="n"/>
       <c r="EN28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EP28" s="18" t="n"/>
+      <c r="EP28" s="43" t="n"/>
       <c r="EU28" s="16" t="n"/>
       <c r="EX28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EZ28" s="18" t="n"/>
+      <c r="EZ28" s="43" t="n"/>
       <c r="FE28" s="16" t="n"/>
       <c r="FH28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="FJ28" s="18" t="n"/>
+      <c r="FJ28" s="43" t="n"/>
       <c r="FO28" s="16" t="n"/>
       <c r="FR28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="FT28" s="18" t="n"/>
+      <c r="FT28" s="43" t="n"/>
       <c r="FY28" s="16" t="n"/>
       <c r="GB28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GD28" s="18" t="n"/>
+      <c r="GD28" s="43" t="n"/>
       <c r="GI28" s="16" t="n"/>
       <c r="GL28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GN28" s="18" t="n"/>
+      <c r="GN28" s="43" t="n"/>
       <c r="GS28" s="16" t="n"/>
       <c r="GV28" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GX28" s="18" t="n"/>
+      <c r="GX28" s="43" t="n"/>
       <c r="HC28" s="16" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -4833,7 +4836,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="E29" s="20" t="n"/>
+      <c r="E29" s="44" t="n"/>
       <c r="L29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4844,7 +4847,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="O29" s="20" t="n"/>
+      <c r="O29" s="44" t="n"/>
       <c r="V29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4855,7 +4858,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="Y29" s="20" t="n"/>
+      <c r="Y29" s="44" t="n"/>
       <c r="AF29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4866,7 +4869,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="AI29" s="20" t="n"/>
+      <c r="AI29" s="44" t="n"/>
       <c r="AP29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4877,7 +4880,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="AS29" s="20" t="n"/>
+      <c r="AS29" s="44" t="n"/>
       <c r="AZ29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4888,7 +4891,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BC29" s="20" t="n"/>
+      <c r="BC29" s="44" t="n"/>
       <c r="BJ29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4899,7 +4902,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BM29" s="20" t="n"/>
+      <c r="BM29" s="44" t="n"/>
       <c r="BT29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4910,7 +4913,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BW29" s="20" t="n"/>
+      <c r="BW29" s="44" t="n"/>
       <c r="CD29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4921,7 +4924,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="CG29" s="20" t="n"/>
+      <c r="CG29" s="44" t="n"/>
       <c r="CN29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4932,7 +4935,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="CQ29" s="20" t="n"/>
+      <c r="CQ29" s="44" t="n"/>
       <c r="CX29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4943,7 +4946,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DA29" s="20" t="n"/>
+      <c r="DA29" s="44" t="n"/>
       <c r="DH29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4954,7 +4957,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DK29" s="20" t="n"/>
+      <c r="DK29" s="44" t="n"/>
       <c r="DR29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4965,7 +4968,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DU29" s="20" t="n"/>
+      <c r="DU29" s="44" t="n"/>
       <c r="EB29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4976,7 +4979,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EE29" s="20" t="n"/>
+      <c r="EE29" s="44" t="n"/>
       <c r="EL29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4987,7 +4990,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EO29" s="20" t="n"/>
+      <c r="EO29" s="44" t="n"/>
       <c r="EV29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -4998,7 +5001,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EY29" s="20" t="n"/>
+      <c r="EY29" s="44" t="n"/>
       <c r="FF29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -5009,7 +5012,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="FI29" s="20" t="n"/>
+      <c r="FI29" s="44" t="n"/>
       <c r="FP29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -5020,7 +5023,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="FS29" s="20" t="n"/>
+      <c r="FS29" s="44" t="n"/>
       <c r="FZ29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -5031,7 +5034,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GC29" s="20" t="n"/>
+      <c r="GC29" s="44" t="n"/>
       <c r="GJ29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -5042,7 +5045,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GM29" s="20" t="n"/>
+      <c r="GM29" s="44" t="n"/>
       <c r="GT29" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -5053,7 +5056,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GW29" s="20" t="n"/>
+      <c r="GW29" s="44" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="B30" s="21" t="n"/>
@@ -5062,147 +5065,147 @@
           <t>月</t>
         </is>
       </c>
-      <c r="E30" s="23" t="n"/>
+      <c r="E30" s="45" t="n"/>
       <c r="L30" s="21" t="n"/>
       <c r="M30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="O30" s="23" t="n"/>
+      <c r="O30" s="45" t="n"/>
       <c r="V30" s="21" t="n"/>
       <c r="W30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="Y30" s="23" t="n"/>
+      <c r="Y30" s="45" t="n"/>
       <c r="AF30" s="21" t="n"/>
       <c r="AG30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AI30" s="23" t="n"/>
+      <c r="AI30" s="45" t="n"/>
       <c r="AP30" s="21" t="n"/>
       <c r="AQ30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AS30" s="23" t="n"/>
+      <c r="AS30" s="45" t="n"/>
       <c r="AZ30" s="21" t="n"/>
       <c r="BA30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BC30" s="23" t="n"/>
+      <c r="BC30" s="45" t="n"/>
       <c r="BJ30" s="21" t="n"/>
       <c r="BK30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BM30" s="23" t="n"/>
+      <c r="BM30" s="45" t="n"/>
       <c r="BT30" s="21" t="n"/>
       <c r="BU30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BW30" s="23" t="n"/>
+      <c r="BW30" s="45" t="n"/>
       <c r="CD30" s="21" t="n"/>
       <c r="CE30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="CG30" s="23" t="n"/>
+      <c r="CG30" s="45" t="n"/>
       <c r="CN30" s="21" t="n"/>
       <c r="CO30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="CQ30" s="23" t="n"/>
+      <c r="CQ30" s="45" t="n"/>
       <c r="CX30" s="21" t="n"/>
       <c r="CY30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DA30" s="23" t="n"/>
+      <c r="DA30" s="45" t="n"/>
       <c r="DH30" s="21" t="n"/>
       <c r="DI30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DK30" s="23" t="n"/>
+      <c r="DK30" s="45" t="n"/>
       <c r="DR30" s="21" t="n"/>
       <c r="DS30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DU30" s="23" t="n"/>
+      <c r="DU30" s="45" t="n"/>
       <c r="EB30" s="21" t="n"/>
       <c r="EC30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EE30" s="23" t="n"/>
+      <c r="EE30" s="45" t="n"/>
       <c r="EL30" s="21" t="n"/>
       <c r="EM30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EO30" s="23" t="n"/>
+      <c r="EO30" s="45" t="n"/>
       <c r="EV30" s="21" t="n"/>
       <c r="EW30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EY30" s="23" t="n"/>
+      <c r="EY30" s="45" t="n"/>
       <c r="FF30" s="21" t="n"/>
       <c r="FG30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="FI30" s="23" t="n"/>
+      <c r="FI30" s="45" t="n"/>
       <c r="FP30" s="21" t="n"/>
       <c r="FQ30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="FS30" s="23" t="n"/>
+      <c r="FS30" s="45" t="n"/>
       <c r="FZ30" s="21" t="n"/>
       <c r="GA30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GC30" s="23" t="n"/>
+      <c r="GC30" s="45" t="n"/>
       <c r="GJ30" s="21" t="n"/>
       <c r="GK30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GM30" s="23" t="n"/>
+      <c r="GM30" s="45" t="n"/>
       <c r="GT30" s="21" t="n"/>
       <c r="GU30" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GW30" s="23" t="n"/>
+      <c r="GW30" s="45" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="B31" s="21" t="n"/>
@@ -5216,7 +5219,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="E31" s="24" t="n"/>
+      <c r="E31" s="46" t="n"/>
       <c r="L31" s="21" t="n"/>
       <c r="M31" s="22" t="inlineStr">
         <is>
@@ -5228,7 +5231,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="O31" s="24" t="n"/>
+      <c r="O31" s="46" t="n"/>
       <c r="V31" s="21" t="n"/>
       <c r="W31" s="22" t="inlineStr">
         <is>
@@ -5240,7 +5243,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="Y31" s="24" t="n"/>
+      <c r="Y31" s="46" t="n"/>
       <c r="AF31" s="21" t="n"/>
       <c r="AG31" s="22" t="inlineStr">
         <is>
@@ -5252,7 +5255,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="AI31" s="24" t="n"/>
+      <c r="AI31" s="46" t="n"/>
       <c r="AP31" s="21" t="n"/>
       <c r="AQ31" s="22" t="inlineStr">
         <is>
@@ -5264,7 +5267,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="AS31" s="24" t="n"/>
+      <c r="AS31" s="46" t="n"/>
       <c r="AZ31" s="21" t="n"/>
       <c r="BA31" s="22" t="inlineStr">
         <is>
@@ -5276,7 +5279,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BC31" s="24" t="n"/>
+      <c r="BC31" s="46" t="n"/>
       <c r="BJ31" s="21" t="n"/>
       <c r="BK31" s="22" t="inlineStr">
         <is>
@@ -5288,7 +5291,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BM31" s="24" t="n"/>
+      <c r="BM31" s="46" t="n"/>
       <c r="BT31" s="21" t="n"/>
       <c r="BU31" s="22" t="inlineStr">
         <is>
@@ -5300,7 +5303,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BW31" s="24" t="n"/>
+      <c r="BW31" s="46" t="n"/>
       <c r="CD31" s="21" t="n"/>
       <c r="CE31" s="22" t="inlineStr">
         <is>
@@ -5312,7 +5315,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="CG31" s="24" t="n"/>
+      <c r="CG31" s="46" t="n"/>
       <c r="CN31" s="21" t="n"/>
       <c r="CO31" s="22" t="inlineStr">
         <is>
@@ -5324,7 +5327,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="CQ31" s="24" t="n"/>
+      <c r="CQ31" s="46" t="n"/>
       <c r="CX31" s="21" t="n"/>
       <c r="CY31" s="22" t="inlineStr">
         <is>
@@ -5336,7 +5339,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DA31" s="24" t="n"/>
+      <c r="DA31" s="46" t="n"/>
       <c r="DH31" s="21" t="n"/>
       <c r="DI31" s="22" t="inlineStr">
         <is>
@@ -5348,7 +5351,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DK31" s="24" t="n"/>
+      <c r="DK31" s="46" t="n"/>
       <c r="DR31" s="21" t="n"/>
       <c r="DS31" s="22" t="inlineStr">
         <is>
@@ -5360,7 +5363,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DU31" s="24" t="n"/>
+      <c r="DU31" s="46" t="n"/>
       <c r="EB31" s="21" t="n"/>
       <c r="EC31" s="22" t="inlineStr">
         <is>
@@ -5372,7 +5375,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EE31" s="24" t="n"/>
+      <c r="EE31" s="46" t="n"/>
       <c r="EL31" s="21" t="n"/>
       <c r="EM31" s="22" t="inlineStr">
         <is>
@@ -5384,7 +5387,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EO31" s="24" t="n"/>
+      <c r="EO31" s="46" t="n"/>
       <c r="EV31" s="21" t="n"/>
       <c r="EW31" s="22" t="inlineStr">
         <is>
@@ -5396,7 +5399,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EY31" s="24" t="n"/>
+      <c r="EY31" s="46" t="n"/>
       <c r="FF31" s="21" t="n"/>
       <c r="FG31" s="22" t="inlineStr">
         <is>
@@ -5408,7 +5411,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="FI31" s="24" t="n"/>
+      <c r="FI31" s="46" t="n"/>
       <c r="FP31" s="21" t="n"/>
       <c r="FQ31" s="22" t="inlineStr">
         <is>
@@ -5420,7 +5423,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="FS31" s="24" t="n"/>
+      <c r="FS31" s="46" t="n"/>
       <c r="FZ31" s="21" t="n"/>
       <c r="GA31" s="22" t="inlineStr">
         <is>
@@ -5432,7 +5435,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GC31" s="24" t="n"/>
+      <c r="GC31" s="46" t="n"/>
       <c r="GJ31" s="21" t="n"/>
       <c r="GK31" s="22" t="inlineStr">
         <is>
@@ -5444,7 +5447,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GM31" s="24" t="n"/>
+      <c r="GM31" s="46" t="n"/>
       <c r="GT31" s="21" t="n"/>
       <c r="GU31" s="22" t="inlineStr">
         <is>
@@ -5456,7 +5459,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GW31" s="24" t="n"/>
+      <c r="GW31" s="46" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="B32" s="25" t="n"/>
@@ -5825,132 +5828,132 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="30" t="inlineStr">
+      <c r="B37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="D37" s="31" t="n"/>
-      <c r="L37" s="30" t="inlineStr">
+      <c r="D37" s="48" t="n"/>
+      <c r="L37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="N37" s="31" t="n"/>
-      <c r="V37" s="30" t="inlineStr">
+      <c r="N37" s="48" t="n"/>
+      <c r="V37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="X37" s="31" t="n"/>
-      <c r="AF37" s="30" t="inlineStr">
+      <c r="X37" s="48" t="n"/>
+      <c r="AF37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="AH37" s="31" t="n"/>
-      <c r="AP37" s="30" t="inlineStr">
+      <c r="AH37" s="48" t="n"/>
+      <c r="AP37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="AR37" s="31" t="n"/>
-      <c r="AZ37" s="30" t="inlineStr">
+      <c r="AR37" s="48" t="n"/>
+      <c r="AZ37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BB37" s="31" t="n"/>
-      <c r="BJ37" s="30" t="inlineStr">
+      <c r="BB37" s="48" t="n"/>
+      <c r="BJ37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BL37" s="31" t="n"/>
-      <c r="BT37" s="30" t="inlineStr">
+      <c r="BL37" s="48" t="n"/>
+      <c r="BT37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BV37" s="31" t="n"/>
-      <c r="CD37" s="30" t="inlineStr">
+      <c r="BV37" s="48" t="n"/>
+      <c r="CD37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CF37" s="31" t="n"/>
-      <c r="CN37" s="30" t="inlineStr">
+      <c r="CF37" s="48" t="n"/>
+      <c r="CN37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CP37" s="31" t="n"/>
-      <c r="CX37" s="30" t="inlineStr">
+      <c r="CP37" s="48" t="n"/>
+      <c r="CX37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CZ37" s="31" t="n"/>
-      <c r="DH37" s="30" t="inlineStr">
+      <c r="CZ37" s="48" t="n"/>
+      <c r="DH37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="DJ37" s="31" t="n"/>
-      <c r="DR37" s="30" t="inlineStr">
+      <c r="DJ37" s="48" t="n"/>
+      <c r="DR37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="DT37" s="31" t="n"/>
-      <c r="EB37" s="30" t="inlineStr">
+      <c r="DT37" s="48" t="n"/>
+      <c r="EB37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="ED37" s="31" t="n"/>
-      <c r="EL37" s="30" t="inlineStr">
+      <c r="ED37" s="48" t="n"/>
+      <c r="EL37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="EN37" s="31" t="n"/>
-      <c r="EV37" s="30" t="inlineStr">
+      <c r="EN37" s="48" t="n"/>
+      <c r="EV37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="EX37" s="31" t="n"/>
-      <c r="FF37" s="30" t="inlineStr">
+      <c r="EX37" s="48" t="n"/>
+      <c r="FF37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="FH37" s="31" t="n"/>
-      <c r="FP37" s="30" t="inlineStr">
+      <c r="FH37" s="48" t="n"/>
+      <c r="FP37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="FR37" s="31" t="n"/>
-      <c r="FZ37" s="30" t="inlineStr">
+      <c r="FR37" s="48" t="n"/>
+      <c r="FZ37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GB37" s="31" t="n"/>
-      <c r="GJ37" s="30" t="inlineStr">
+      <c r="GB37" s="48" t="n"/>
+      <c r="GJ37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GL37" s="31" t="n"/>
-      <c r="GT37" s="30" t="inlineStr">
+      <c r="GL37" s="48" t="n"/>
+      <c r="GT37" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GV37" s="31" t="n"/>
+      <c r="GV37" s="48" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="B38" s="32" t="inlineStr">
@@ -5958,299 +5961,299 @@
           <t>欠席</t>
         </is>
       </c>
-      <c r="C38" s="20" t="n"/>
+      <c r="C38" s="44" t="n"/>
       <c r="L38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="M38" s="20" t="n"/>
+      <c r="M38" s="44" t="n"/>
       <c r="V38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="W38" s="20" t="n"/>
+      <c r="W38" s="44" t="n"/>
       <c r="AF38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="AG38" s="20" t="n"/>
+      <c r="AG38" s="44" t="n"/>
       <c r="AP38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="AQ38" s="20" t="n"/>
+      <c r="AQ38" s="44" t="n"/>
       <c r="AZ38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BA38" s="20" t="n"/>
+      <c r="BA38" s="44" t="n"/>
       <c r="BJ38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BK38" s="20" t="n"/>
+      <c r="BK38" s="44" t="n"/>
       <c r="BT38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BU38" s="20" t="n"/>
+      <c r="BU38" s="44" t="n"/>
       <c r="CD38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CE38" s="20" t="n"/>
+      <c r="CE38" s="44" t="n"/>
       <c r="CN38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CO38" s="20" t="n"/>
+      <c r="CO38" s="44" t="n"/>
       <c r="CX38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CY38" s="20" t="n"/>
+      <c r="CY38" s="44" t="n"/>
       <c r="DH38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="DI38" s="20" t="n"/>
+      <c r="DI38" s="44" t="n"/>
       <c r="DR38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="DS38" s="20" t="n"/>
+      <c r="DS38" s="44" t="n"/>
       <c r="EB38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EC38" s="20" t="n"/>
+      <c r="EC38" s="44" t="n"/>
       <c r="EL38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EM38" s="20" t="n"/>
+      <c r="EM38" s="44" t="n"/>
       <c r="EV38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EW38" s="20" t="n"/>
+      <c r="EW38" s="44" t="n"/>
       <c r="FF38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="FG38" s="20" t="n"/>
+      <c r="FG38" s="44" t="n"/>
       <c r="FP38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="FQ38" s="20" t="n"/>
+      <c r="FQ38" s="44" t="n"/>
       <c r="FZ38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GA38" s="20" t="n"/>
+      <c r="GA38" s="44" t="n"/>
       <c r="GJ38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GK38" s="20" t="n"/>
+      <c r="GK38" s="44" t="n"/>
       <c r="GT38" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GU38" s="20" t="n"/>
+      <c r="GU38" s="44" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="C39" s="33" t="n"/>
-      <c r="M39" s="33" t="n"/>
-      <c r="W39" s="33" t="n"/>
-      <c r="AG39" s="33" t="n"/>
-      <c r="AQ39" s="33" t="n"/>
-      <c r="BA39" s="33" t="n"/>
-      <c r="BK39" s="33" t="n"/>
-      <c r="BU39" s="33" t="n"/>
-      <c r="CE39" s="33" t="n"/>
-      <c r="CO39" s="33" t="n"/>
-      <c r="CY39" s="33" t="n"/>
-      <c r="DI39" s="33" t="n"/>
-      <c r="DS39" s="33" t="n"/>
-      <c r="EC39" s="33" t="n"/>
-      <c r="EM39" s="33" t="n"/>
-      <c r="EW39" s="33" t="n"/>
-      <c r="FG39" s="33" t="n"/>
-      <c r="FQ39" s="33" t="n"/>
-      <c r="GA39" s="33" t="n"/>
-      <c r="GK39" s="33" t="n"/>
-      <c r="GU39" s="33" t="n"/>
+      <c r="C39" s="49" t="n"/>
+      <c r="M39" s="49" t="n"/>
+      <c r="W39" s="49" t="n"/>
+      <c r="AG39" s="49" t="n"/>
+      <c r="AQ39" s="49" t="n"/>
+      <c r="BA39" s="49" t="n"/>
+      <c r="BK39" s="49" t="n"/>
+      <c r="BU39" s="49" t="n"/>
+      <c r="CE39" s="49" t="n"/>
+      <c r="CO39" s="49" t="n"/>
+      <c r="CY39" s="49" t="n"/>
+      <c r="DI39" s="49" t="n"/>
+      <c r="DS39" s="49" t="n"/>
+      <c r="EC39" s="49" t="n"/>
+      <c r="EM39" s="49" t="n"/>
+      <c r="EW39" s="49" t="n"/>
+      <c r="FG39" s="49" t="n"/>
+      <c r="FQ39" s="49" t="n"/>
+      <c r="GA39" s="49" t="n"/>
+      <c r="GK39" s="49" t="n"/>
+      <c r="GU39" s="49" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="B40" s="34" t="inlineStr">
+      <c r="B40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="H40" s="35" t="n"/>
-      <c r="I40" s="36" t="n"/>
-      <c r="L40" s="34" t="inlineStr">
+      <c r="H40" s="51" t="n"/>
+      <c r="I40" s="52" t="n"/>
+      <c r="L40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="R40" s="35" t="n"/>
-      <c r="S40" s="36" t="n"/>
-      <c r="V40" s="34" t="inlineStr">
+      <c r="R40" s="51" t="n"/>
+      <c r="S40" s="52" t="n"/>
+      <c r="V40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AB40" s="35" t="n"/>
-      <c r="AC40" s="36" t="n"/>
-      <c r="AF40" s="34" t="inlineStr">
+      <c r="AB40" s="51" t="n"/>
+      <c r="AC40" s="52" t="n"/>
+      <c r="AF40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AL40" s="35" t="n"/>
-      <c r="AM40" s="36" t="n"/>
-      <c r="AP40" s="34" t="inlineStr">
+      <c r="AL40" s="51" t="n"/>
+      <c r="AM40" s="52" t="n"/>
+      <c r="AP40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AV40" s="35" t="n"/>
-      <c r="AW40" s="36" t="n"/>
-      <c r="AZ40" s="34" t="inlineStr">
+      <c r="AV40" s="51" t="n"/>
+      <c r="AW40" s="52" t="n"/>
+      <c r="AZ40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BF40" s="35" t="n"/>
-      <c r="BG40" s="36" t="n"/>
-      <c r="BJ40" s="34" t="inlineStr">
+      <c r="BF40" s="51" t="n"/>
+      <c r="BG40" s="52" t="n"/>
+      <c r="BJ40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BP40" s="35" t="n"/>
-      <c r="BQ40" s="36" t="n"/>
-      <c r="BT40" s="34" t="inlineStr">
+      <c r="BP40" s="51" t="n"/>
+      <c r="BQ40" s="52" t="n"/>
+      <c r="BT40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BZ40" s="35" t="n"/>
-      <c r="CA40" s="36" t="n"/>
-      <c r="CD40" s="34" t="inlineStr">
+      <c r="BZ40" s="51" t="n"/>
+      <c r="CA40" s="52" t="n"/>
+      <c r="CD40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="CJ40" s="35" t="n"/>
-      <c r="CK40" s="36" t="n"/>
-      <c r="CN40" s="34" t="inlineStr">
+      <c r="CJ40" s="51" t="n"/>
+      <c r="CK40" s="52" t="n"/>
+      <c r="CN40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="CT40" s="35" t="n"/>
-      <c r="CU40" s="36" t="n"/>
-      <c r="CX40" s="34" t="inlineStr">
+      <c r="CT40" s="51" t="n"/>
+      <c r="CU40" s="52" t="n"/>
+      <c r="CX40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DD40" s="35" t="n"/>
-      <c r="DE40" s="36" t="n"/>
-      <c r="DH40" s="34" t="inlineStr">
+      <c r="DD40" s="51" t="n"/>
+      <c r="DE40" s="52" t="n"/>
+      <c r="DH40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DN40" s="35" t="n"/>
-      <c r="DO40" s="36" t="n"/>
-      <c r="DR40" s="34" t="inlineStr">
+      <c r="DN40" s="51" t="n"/>
+      <c r="DO40" s="52" t="n"/>
+      <c r="DR40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DX40" s="35" t="n"/>
-      <c r="DY40" s="36" t="n"/>
-      <c r="EB40" s="34" t="inlineStr">
+      <c r="DX40" s="51" t="n"/>
+      <c r="DY40" s="52" t="n"/>
+      <c r="EB40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="EH40" s="35" t="n"/>
-      <c r="EI40" s="36" t="n"/>
-      <c r="EL40" s="34" t="inlineStr">
+      <c r="EH40" s="51" t="n"/>
+      <c r="EI40" s="52" t="n"/>
+      <c r="EL40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="ER40" s="35" t="n"/>
-      <c r="ES40" s="36" t="n"/>
-      <c r="EV40" s="34" t="inlineStr">
+      <c r="ER40" s="51" t="n"/>
+      <c r="ES40" s="52" t="n"/>
+      <c r="EV40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FB40" s="35" t="n"/>
-      <c r="FC40" s="36" t="n"/>
-      <c r="FF40" s="34" t="inlineStr">
+      <c r="FB40" s="51" t="n"/>
+      <c r="FC40" s="52" t="n"/>
+      <c r="FF40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FL40" s="35" t="n"/>
-      <c r="FM40" s="36" t="n"/>
-      <c r="FP40" s="34" t="inlineStr">
+      <c r="FL40" s="51" t="n"/>
+      <c r="FM40" s="52" t="n"/>
+      <c r="FP40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FV40" s="35" t="n"/>
-      <c r="FW40" s="36" t="n"/>
-      <c r="FZ40" s="34" t="inlineStr">
+      <c r="FV40" s="51" t="n"/>
+      <c r="FW40" s="52" t="n"/>
+      <c r="FZ40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GF40" s="35" t="n"/>
-      <c r="GG40" s="36" t="n"/>
-      <c r="GJ40" s="34" t="inlineStr">
+      <c r="GF40" s="51" t="n"/>
+      <c r="GG40" s="52" t="n"/>
+      <c r="GJ40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GP40" s="35" t="n"/>
-      <c r="GQ40" s="36" t="n"/>
-      <c r="GT40" s="34" t="inlineStr">
+      <c r="GP40" s="51" t="n"/>
+      <c r="GQ40" s="52" t="n"/>
+      <c r="GT40" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GZ40" s="35" t="n"/>
-      <c r="HA40" s="36" t="n"/>
+      <c r="GZ40" s="51" t="n"/>
+      <c r="HA40" s="52" t="n"/>
     </row>
     <row r="41" ht="12" customHeight="1">
       <c r="B41" s="37" t="inlineStr">
@@ -6258,127 +6261,127 @@
           <t>備考</t>
         </is>
       </c>
-      <c r="C41" s="38" t="n"/>
+      <c r="C41" s="53" t="n"/>
       <c r="L41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="M41" s="38" t="n"/>
+      <c r="M41" s="53" t="n"/>
       <c r="V41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="W41" s="38" t="n"/>
+      <c r="W41" s="53" t="n"/>
       <c r="AF41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="AG41" s="38" t="n"/>
+      <c r="AG41" s="53" t="n"/>
       <c r="AP41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="AQ41" s="38" t="n"/>
+      <c r="AQ41" s="53" t="n"/>
       <c r="AZ41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BA41" s="38" t="n"/>
+      <c r="BA41" s="53" t="n"/>
       <c r="BJ41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BK41" s="38" t="n"/>
+      <c r="BK41" s="53" t="n"/>
       <c r="BT41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BU41" s="38" t="n"/>
+      <c r="BU41" s="53" t="n"/>
       <c r="CD41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CE41" s="38" t="n"/>
+      <c r="CE41" s="53" t="n"/>
       <c r="CN41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CO41" s="38" t="n"/>
+      <c r="CO41" s="53" t="n"/>
       <c r="CX41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CY41" s="38" t="n"/>
+      <c r="CY41" s="53" t="n"/>
       <c r="DH41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="DI41" s="38" t="n"/>
+      <c r="DI41" s="53" t="n"/>
       <c r="DR41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="DS41" s="38" t="n"/>
+      <c r="DS41" s="53" t="n"/>
       <c r="EB41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EC41" s="38" t="n"/>
+      <c r="EC41" s="53" t="n"/>
       <c r="EL41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EM41" s="38" t="n"/>
+      <c r="EM41" s="53" t="n"/>
       <c r="EV41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EW41" s="38" t="n"/>
+      <c r="EW41" s="53" t="n"/>
       <c r="FF41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="FG41" s="38" t="n"/>
+      <c r="FG41" s="53" t="n"/>
       <c r="FP41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="FQ41" s="38" t="n"/>
+      <c r="FQ41" s="53" t="n"/>
       <c r="FZ41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GA41" s="38" t="n"/>
+      <c r="GA41" s="53" t="n"/>
       <c r="GJ41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GK41" s="38" t="n"/>
+      <c r="GK41" s="53" t="n"/>
       <c r="GT41" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GU41" s="38" t="n"/>
+      <c r="GU41" s="53" t="n"/>
     </row>
     <row r="42" ht="12" customHeight="1"/>
     <row r="43" ht="12" customHeight="1"/>
@@ -6788,67 +6791,67 @@
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="B47" s="14" t="n"/>
-      <c r="D47" s="15" t="n"/>
+      <c r="D47" s="42" t="n"/>
       <c r="K47" s="16" t="n"/>
       <c r="L47" s="14" t="n"/>
-      <c r="N47" s="15" t="n"/>
+      <c r="N47" s="42" t="n"/>
       <c r="U47" s="16" t="n"/>
       <c r="V47" s="14" t="n"/>
-      <c r="X47" s="15" t="n"/>
+      <c r="X47" s="42" t="n"/>
       <c r="AE47" s="16" t="n"/>
       <c r="AF47" s="14" t="n"/>
-      <c r="AH47" s="15" t="n"/>
+      <c r="AH47" s="42" t="n"/>
       <c r="AO47" s="16" t="n"/>
       <c r="AP47" s="14" t="n"/>
-      <c r="AR47" s="15" t="n"/>
+      <c r="AR47" s="42" t="n"/>
       <c r="AY47" s="16" t="n"/>
       <c r="AZ47" s="14" t="n"/>
-      <c r="BB47" s="15" t="n"/>
+      <c r="BB47" s="42" t="n"/>
       <c r="BI47" s="16" t="n"/>
       <c r="BJ47" s="14" t="n"/>
-      <c r="BL47" s="15" t="n"/>
+      <c r="BL47" s="42" t="n"/>
       <c r="BS47" s="16" t="n"/>
       <c r="BT47" s="14" t="n"/>
-      <c r="BV47" s="15" t="n"/>
+      <c r="BV47" s="42" t="n"/>
       <c r="CC47" s="16" t="n"/>
       <c r="CD47" s="14" t="n"/>
-      <c r="CF47" s="15" t="n"/>
+      <c r="CF47" s="42" t="n"/>
       <c r="CM47" s="16" t="n"/>
       <c r="CN47" s="14" t="n"/>
-      <c r="CP47" s="15" t="n"/>
+      <c r="CP47" s="42" t="n"/>
       <c r="CW47" s="16" t="n"/>
       <c r="CX47" s="14" t="n"/>
-      <c r="CZ47" s="15" t="n"/>
+      <c r="CZ47" s="42" t="n"/>
       <c r="DG47" s="16" t="n"/>
       <c r="DH47" s="14" t="n"/>
-      <c r="DJ47" s="15" t="n"/>
+      <c r="DJ47" s="42" t="n"/>
       <c r="DQ47" s="16" t="n"/>
       <c r="DR47" s="14" t="n"/>
-      <c r="DT47" s="15" t="n"/>
+      <c r="DT47" s="42" t="n"/>
       <c r="EA47" s="16" t="n"/>
       <c r="EB47" s="14" t="n"/>
-      <c r="ED47" s="15" t="n"/>
+      <c r="ED47" s="42" t="n"/>
       <c r="EK47" s="16" t="n"/>
       <c r="EL47" s="14" t="n"/>
-      <c r="EN47" s="15" t="n"/>
+      <c r="EN47" s="42" t="n"/>
       <c r="EU47" s="16" t="n"/>
       <c r="EV47" s="14" t="n"/>
-      <c r="EX47" s="15" t="n"/>
+      <c r="EX47" s="42" t="n"/>
       <c r="FE47" s="16" t="n"/>
       <c r="FF47" s="14" t="n"/>
-      <c r="FH47" s="15" t="n"/>
+      <c r="FH47" s="42" t="n"/>
       <c r="FO47" s="16" t="n"/>
       <c r="FP47" s="14" t="n"/>
-      <c r="FR47" s="15" t="n"/>
+      <c r="FR47" s="42" t="n"/>
       <c r="FY47" s="16" t="n"/>
       <c r="FZ47" s="14" t="n"/>
-      <c r="GB47" s="15" t="n"/>
+      <c r="GB47" s="42" t="n"/>
       <c r="GI47" s="16" t="n"/>
       <c r="GJ47" s="14" t="n"/>
-      <c r="GL47" s="15" t="n"/>
+      <c r="GL47" s="42" t="n"/>
       <c r="GS47" s="16" t="n"/>
       <c r="GT47" s="14" t="n"/>
-      <c r="GV47" s="15" t="n"/>
+      <c r="GV47" s="42" t="n"/>
       <c r="HC47" s="16" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
@@ -6857,147 +6860,147 @@
           <t>ページ</t>
         </is>
       </c>
-      <c r="F48" s="18" t="n"/>
+      <c r="F48" s="43" t="n"/>
       <c r="K48" s="16" t="n"/>
       <c r="N48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="P48" s="18" t="n"/>
+      <c r="P48" s="43" t="n"/>
       <c r="U48" s="16" t="n"/>
       <c r="X48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="Z48" s="18" t="n"/>
+      <c r="Z48" s="43" t="n"/>
       <c r="AE48" s="16" t="n"/>
       <c r="AH48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="AJ48" s="18" t="n"/>
+      <c r="AJ48" s="43" t="n"/>
       <c r="AO48" s="16" t="n"/>
       <c r="AR48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="AT48" s="18" t="n"/>
+      <c r="AT48" s="43" t="n"/>
       <c r="AY48" s="16" t="n"/>
       <c r="BB48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BD48" s="18" t="n"/>
+      <c r="BD48" s="43" t="n"/>
       <c r="BI48" s="16" t="n"/>
       <c r="BL48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BN48" s="18" t="n"/>
+      <c r="BN48" s="43" t="n"/>
       <c r="BS48" s="16" t="n"/>
       <c r="BV48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="BX48" s="18" t="n"/>
+      <c r="BX48" s="43" t="n"/>
       <c r="CC48" s="16" t="n"/>
       <c r="CF48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="CH48" s="18" t="n"/>
+      <c r="CH48" s="43" t="n"/>
       <c r="CM48" s="16" t="n"/>
       <c r="CP48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="CR48" s="18" t="n"/>
+      <c r="CR48" s="43" t="n"/>
       <c r="CW48" s="16" t="n"/>
       <c r="CZ48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DB48" s="18" t="n"/>
+      <c r="DB48" s="43" t="n"/>
       <c r="DG48" s="16" t="n"/>
       <c r="DJ48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DL48" s="18" t="n"/>
+      <c r="DL48" s="43" t="n"/>
       <c r="DQ48" s="16" t="n"/>
       <c r="DT48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="DV48" s="18" t="n"/>
+      <c r="DV48" s="43" t="n"/>
       <c r="EA48" s="16" t="n"/>
       <c r="ED48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EF48" s="18" t="n"/>
+      <c r="EF48" s="43" t="n"/>
       <c r="EK48" s="16" t="n"/>
       <c r="EN48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EP48" s="18" t="n"/>
+      <c r="EP48" s="43" t="n"/>
       <c r="EU48" s="16" t="n"/>
       <c r="EX48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="EZ48" s="18" t="n"/>
+      <c r="EZ48" s="43" t="n"/>
       <c r="FE48" s="16" t="n"/>
       <c r="FH48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="FJ48" s="18" t="n"/>
+      <c r="FJ48" s="43" t="n"/>
       <c r="FO48" s="16" t="n"/>
       <c r="FR48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="FT48" s="18" t="n"/>
+      <c r="FT48" s="43" t="n"/>
       <c r="FY48" s="16" t="n"/>
       <c r="GB48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GD48" s="18" t="n"/>
+      <c r="GD48" s="43" t="n"/>
       <c r="GI48" s="16" t="n"/>
       <c r="GL48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GN48" s="18" t="n"/>
+      <c r="GN48" s="43" t="n"/>
       <c r="GS48" s="16" t="n"/>
       <c r="GV48" s="17" t="inlineStr">
         <is>
           <t>ページ</t>
         </is>
       </c>
-      <c r="GX48" s="18" t="n"/>
+      <c r="GX48" s="43" t="n"/>
       <c r="HC48" s="16" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
@@ -7011,7 +7014,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="E49" s="20" t="n"/>
+      <c r="E49" s="44" t="n"/>
       <c r="L49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7022,7 +7025,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="O49" s="20" t="n"/>
+      <c r="O49" s="44" t="n"/>
       <c r="V49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7033,7 +7036,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="Y49" s="20" t="n"/>
+      <c r="Y49" s="44" t="n"/>
       <c r="AF49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7044,7 +7047,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="AI49" s="20" t="n"/>
+      <c r="AI49" s="44" t="n"/>
       <c r="AP49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7055,7 +7058,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="AS49" s="20" t="n"/>
+      <c r="AS49" s="44" t="n"/>
       <c r="AZ49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7066,7 +7069,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BC49" s="20" t="n"/>
+      <c r="BC49" s="44" t="n"/>
       <c r="BJ49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7077,7 +7080,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BM49" s="20" t="n"/>
+      <c r="BM49" s="44" t="n"/>
       <c r="BT49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7088,7 +7091,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="BW49" s="20" t="n"/>
+      <c r="BW49" s="44" t="n"/>
       <c r="CD49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7099,7 +7102,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="CG49" s="20" t="n"/>
+      <c r="CG49" s="44" t="n"/>
       <c r="CN49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7110,7 +7113,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="CQ49" s="20" t="n"/>
+      <c r="CQ49" s="44" t="n"/>
       <c r="CX49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7121,7 +7124,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DA49" s="20" t="n"/>
+      <c r="DA49" s="44" t="n"/>
       <c r="DH49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7132,7 +7135,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DK49" s="20" t="n"/>
+      <c r="DK49" s="44" t="n"/>
       <c r="DR49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7143,7 +7146,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="DU49" s="20" t="n"/>
+      <c r="DU49" s="44" t="n"/>
       <c r="EB49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7154,7 +7157,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EE49" s="20" t="n"/>
+      <c r="EE49" s="44" t="n"/>
       <c r="EL49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7165,7 +7168,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EO49" s="20" t="n"/>
+      <c r="EO49" s="44" t="n"/>
       <c r="EV49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7176,7 +7179,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="EY49" s="20" t="n"/>
+      <c r="EY49" s="44" t="n"/>
       <c r="FF49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7187,7 +7190,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="FI49" s="20" t="n"/>
+      <c r="FI49" s="44" t="n"/>
       <c r="FP49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7198,7 +7201,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="FS49" s="20" t="n"/>
+      <c r="FS49" s="44" t="n"/>
       <c r="FZ49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7209,7 +7212,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GC49" s="20" t="n"/>
+      <c r="GC49" s="44" t="n"/>
       <c r="GJ49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7220,7 +7223,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GM49" s="20" t="n"/>
+      <c r="GM49" s="44" t="n"/>
       <c r="GT49" s="12" t="inlineStr">
         <is>
           <t>授業日</t>
@@ -7231,7 +7234,7 @@
           <t>宿題</t>
         </is>
       </c>
-      <c r="GW49" s="20" t="n"/>
+      <c r="GW49" s="44" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="B50" s="21" t="n"/>
@@ -7240,147 +7243,147 @@
           <t>月</t>
         </is>
       </c>
-      <c r="E50" s="23" t="n"/>
+      <c r="E50" s="45" t="n"/>
       <c r="L50" s="21" t="n"/>
       <c r="M50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="O50" s="23" t="n"/>
+      <c r="O50" s="45" t="n"/>
       <c r="V50" s="21" t="n"/>
       <c r="W50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="Y50" s="23" t="n"/>
+      <c r="Y50" s="45" t="n"/>
       <c r="AF50" s="21" t="n"/>
       <c r="AG50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AI50" s="23" t="n"/>
+      <c r="AI50" s="45" t="n"/>
       <c r="AP50" s="21" t="n"/>
       <c r="AQ50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="AS50" s="23" t="n"/>
+      <c r="AS50" s="45" t="n"/>
       <c r="AZ50" s="21" t="n"/>
       <c r="BA50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BC50" s="23" t="n"/>
+      <c r="BC50" s="45" t="n"/>
       <c r="BJ50" s="21" t="n"/>
       <c r="BK50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BM50" s="23" t="n"/>
+      <c r="BM50" s="45" t="n"/>
       <c r="BT50" s="21" t="n"/>
       <c r="BU50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="BW50" s="23" t="n"/>
+      <c r="BW50" s="45" t="n"/>
       <c r="CD50" s="21" t="n"/>
       <c r="CE50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="CG50" s="23" t="n"/>
+      <c r="CG50" s="45" t="n"/>
       <c r="CN50" s="21" t="n"/>
       <c r="CO50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="CQ50" s="23" t="n"/>
+      <c r="CQ50" s="45" t="n"/>
       <c r="CX50" s="21" t="n"/>
       <c r="CY50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DA50" s="23" t="n"/>
+      <c r="DA50" s="45" t="n"/>
       <c r="DH50" s="21" t="n"/>
       <c r="DI50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DK50" s="23" t="n"/>
+      <c r="DK50" s="45" t="n"/>
       <c r="DR50" s="21" t="n"/>
       <c r="DS50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="DU50" s="23" t="n"/>
+      <c r="DU50" s="45" t="n"/>
       <c r="EB50" s="21" t="n"/>
       <c r="EC50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EE50" s="23" t="n"/>
+      <c r="EE50" s="45" t="n"/>
       <c r="EL50" s="21" t="n"/>
       <c r="EM50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EO50" s="23" t="n"/>
+      <c r="EO50" s="45" t="n"/>
       <c r="EV50" s="21" t="n"/>
       <c r="EW50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="EY50" s="23" t="n"/>
+      <c r="EY50" s="45" t="n"/>
       <c r="FF50" s="21" t="n"/>
       <c r="FG50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="FI50" s="23" t="n"/>
+      <c r="FI50" s="45" t="n"/>
       <c r="FP50" s="21" t="n"/>
       <c r="FQ50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="FS50" s="23" t="n"/>
+      <c r="FS50" s="45" t="n"/>
       <c r="FZ50" s="21" t="n"/>
       <c r="GA50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GC50" s="23" t="n"/>
+      <c r="GC50" s="45" t="n"/>
       <c r="GJ50" s="21" t="n"/>
       <c r="GK50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GM50" s="23" t="n"/>
+      <c r="GM50" s="45" t="n"/>
       <c r="GT50" s="21" t="n"/>
       <c r="GU50" s="22" t="inlineStr">
         <is>
           <t>月</t>
         </is>
       </c>
-      <c r="GW50" s="23" t="n"/>
+      <c r="GW50" s="45" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="B51" s="21" t="n"/>
@@ -7394,7 +7397,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="E51" s="24" t="n"/>
+      <c r="E51" s="46" t="n"/>
       <c r="L51" s="21" t="n"/>
       <c r="M51" s="22" t="inlineStr">
         <is>
@@ -7406,7 +7409,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="O51" s="24" t="n"/>
+      <c r="O51" s="46" t="n"/>
       <c r="V51" s="21" t="n"/>
       <c r="W51" s="22" t="inlineStr">
         <is>
@@ -7418,7 +7421,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="Y51" s="24" t="n"/>
+      <c r="Y51" s="46" t="n"/>
       <c r="AF51" s="21" t="n"/>
       <c r="AG51" s="22" t="inlineStr">
         <is>
@@ -7430,7 +7433,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="AI51" s="24" t="n"/>
+      <c r="AI51" s="46" t="n"/>
       <c r="AP51" s="21" t="n"/>
       <c r="AQ51" s="22" t="inlineStr">
         <is>
@@ -7442,7 +7445,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="AS51" s="24" t="n"/>
+      <c r="AS51" s="46" t="n"/>
       <c r="AZ51" s="21" t="n"/>
       <c r="BA51" s="22" t="inlineStr">
         <is>
@@ -7454,7 +7457,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BC51" s="24" t="n"/>
+      <c r="BC51" s="46" t="n"/>
       <c r="BJ51" s="21" t="n"/>
       <c r="BK51" s="22" t="inlineStr">
         <is>
@@ -7466,7 +7469,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BM51" s="24" t="n"/>
+      <c r="BM51" s="46" t="n"/>
       <c r="BT51" s="21" t="n"/>
       <c r="BU51" s="22" t="inlineStr">
         <is>
@@ -7478,7 +7481,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="BW51" s="24" t="n"/>
+      <c r="BW51" s="46" t="n"/>
       <c r="CD51" s="21" t="n"/>
       <c r="CE51" s="22" t="inlineStr">
         <is>
@@ -7490,7 +7493,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="CG51" s="24" t="n"/>
+      <c r="CG51" s="46" t="n"/>
       <c r="CN51" s="21" t="n"/>
       <c r="CO51" s="22" t="inlineStr">
         <is>
@@ -7502,7 +7505,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="CQ51" s="24" t="n"/>
+      <c r="CQ51" s="46" t="n"/>
       <c r="CX51" s="21" t="n"/>
       <c r="CY51" s="22" t="inlineStr">
         <is>
@@ -7514,7 +7517,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DA51" s="24" t="n"/>
+      <c r="DA51" s="46" t="n"/>
       <c r="DH51" s="21" t="n"/>
       <c r="DI51" s="22" t="inlineStr">
         <is>
@@ -7526,7 +7529,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DK51" s="24" t="n"/>
+      <c r="DK51" s="46" t="n"/>
       <c r="DR51" s="21" t="n"/>
       <c r="DS51" s="22" t="inlineStr">
         <is>
@@ -7538,7 +7541,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="DU51" s="24" t="n"/>
+      <c r="DU51" s="46" t="n"/>
       <c r="EB51" s="21" t="n"/>
       <c r="EC51" s="22" t="inlineStr">
         <is>
@@ -7550,7 +7553,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EE51" s="24" t="n"/>
+      <c r="EE51" s="46" t="n"/>
       <c r="EL51" s="21" t="n"/>
       <c r="EM51" s="22" t="inlineStr">
         <is>
@@ -7562,7 +7565,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EO51" s="24" t="n"/>
+      <c r="EO51" s="46" t="n"/>
       <c r="EV51" s="21" t="n"/>
       <c r="EW51" s="22" t="inlineStr">
         <is>
@@ -7574,7 +7577,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="EY51" s="24" t="n"/>
+      <c r="EY51" s="46" t="n"/>
       <c r="FF51" s="21" t="n"/>
       <c r="FG51" s="22" t="inlineStr">
         <is>
@@ -7586,7 +7589,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="FI51" s="24" t="n"/>
+      <c r="FI51" s="46" t="n"/>
       <c r="FP51" s="21" t="n"/>
       <c r="FQ51" s="22" t="inlineStr">
         <is>
@@ -7598,7 +7601,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="FS51" s="24" t="n"/>
+      <c r="FS51" s="46" t="n"/>
       <c r="FZ51" s="21" t="n"/>
       <c r="GA51" s="22" t="inlineStr">
         <is>
@@ -7610,7 +7613,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GC51" s="24" t="n"/>
+      <c r="GC51" s="46" t="n"/>
       <c r="GJ51" s="21" t="n"/>
       <c r="GK51" s="22" t="inlineStr">
         <is>
@@ -7622,7 +7625,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GM51" s="24" t="n"/>
+      <c r="GM51" s="46" t="n"/>
       <c r="GT51" s="21" t="n"/>
       <c r="GU51" s="22" t="inlineStr">
         <is>
@@ -7634,7 +7637,7 @@
           <t>記録</t>
         </is>
       </c>
-      <c r="GW51" s="24" t="n"/>
+      <c r="GW51" s="46" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="B52" s="25" t="n"/>
@@ -8003,136 +8006,136 @@
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="B57" s="30" t="inlineStr">
+      <c r="B57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="D57" s="41" t="inlineStr">
+      <c r="D57" s="54" t="inlineStr">
         <is>
           <t>https://us06web.zoom.us/rec/share/sI9IzvxjxYkwq_9YMkRHiZAlECNbXhUNia1SC_aSeRM4ExEbc2Ynn-XsX6Yragc.kko9POxRgfqf6gTF?startTime=1782984923000</t>
         </is>
       </c>
-      <c r="L57" s="30" t="inlineStr">
+      <c r="L57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="N57" s="41" t="n"/>
-      <c r="V57" s="30" t="inlineStr">
+      <c r="N57" s="54" t="n"/>
+      <c r="V57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="X57" s="41" t="n"/>
-      <c r="AF57" s="30" t="inlineStr">
+      <c r="X57" s="54" t="n"/>
+      <c r="AF57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="AH57" s="41" t="n"/>
-      <c r="AP57" s="30" t="inlineStr">
+      <c r="AH57" s="54" t="n"/>
+      <c r="AP57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="AR57" s="41" t="n"/>
-      <c r="AZ57" s="30" t="inlineStr">
+      <c r="AR57" s="54" t="n"/>
+      <c r="AZ57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BB57" s="41" t="n"/>
-      <c r="BJ57" s="30" t="inlineStr">
+      <c r="BB57" s="54" t="n"/>
+      <c r="BJ57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BL57" s="41" t="n"/>
-      <c r="BT57" s="30" t="inlineStr">
+      <c r="BL57" s="54" t="n"/>
+      <c r="BT57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="BV57" s="41" t="n"/>
-      <c r="CD57" s="30" t="inlineStr">
+      <c r="BV57" s="54" t="n"/>
+      <c r="CD57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CF57" s="41" t="n"/>
-      <c r="CN57" s="30" t="inlineStr">
+      <c r="CF57" s="54" t="n"/>
+      <c r="CN57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CP57" s="41" t="n"/>
-      <c r="CX57" s="30" t="inlineStr">
+      <c r="CP57" s="54" t="n"/>
+      <c r="CX57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="CZ57" s="41" t="n"/>
-      <c r="DH57" s="30" t="inlineStr">
+      <c r="CZ57" s="54" t="n"/>
+      <c r="DH57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="DJ57" s="41" t="n"/>
-      <c r="DR57" s="30" t="inlineStr">
+      <c r="DJ57" s="54" t="n"/>
+      <c r="DR57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="DT57" s="41" t="n"/>
-      <c r="EB57" s="30" t="inlineStr">
+      <c r="DT57" s="54" t="n"/>
+      <c r="EB57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="ED57" s="41" t="n"/>
-      <c r="EL57" s="30" t="inlineStr">
+      <c r="ED57" s="54" t="n"/>
+      <c r="EL57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="EN57" s="41" t="n"/>
-      <c r="EV57" s="30" t="inlineStr">
+      <c r="EN57" s="54" t="n"/>
+      <c r="EV57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="EX57" s="41" t="n"/>
-      <c r="FF57" s="30" t="inlineStr">
+      <c r="EX57" s="54" t="n"/>
+      <c r="FF57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="FH57" s="41" t="n"/>
-      <c r="FP57" s="30" t="inlineStr">
+      <c r="FH57" s="54" t="n"/>
+      <c r="FP57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="FR57" s="41" t="n"/>
-      <c r="FZ57" s="30" t="inlineStr">
+      <c r="FR57" s="54" t="n"/>
+      <c r="FZ57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GB57" s="41" t="n"/>
-      <c r="GJ57" s="30" t="inlineStr">
+      <c r="GB57" s="54" t="n"/>
+      <c r="GJ57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GL57" s="41" t="n"/>
-      <c r="GT57" s="30" t="inlineStr">
+      <c r="GL57" s="54" t="n"/>
+      <c r="GT57" s="47" t="inlineStr">
         <is>
           <t>録画</t>
         </is>
       </c>
-      <c r="GV57" s="41" t="n"/>
+      <c r="GV57" s="54" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="B58" s="32" t="inlineStr">
@@ -8140,299 +8143,299 @@
           <t>欠席</t>
         </is>
       </c>
-      <c r="C58" s="20" t="n"/>
+      <c r="C58" s="44" t="n"/>
       <c r="L58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="M58" s="20" t="n"/>
+      <c r="M58" s="44" t="n"/>
       <c r="V58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="W58" s="20" t="n"/>
+      <c r="W58" s="44" t="n"/>
       <c r="AF58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="AG58" s="20" t="n"/>
+      <c r="AG58" s="44" t="n"/>
       <c r="AP58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="AQ58" s="20" t="n"/>
+      <c r="AQ58" s="44" t="n"/>
       <c r="AZ58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BA58" s="20" t="n"/>
+      <c r="BA58" s="44" t="n"/>
       <c r="BJ58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BK58" s="20" t="n"/>
+      <c r="BK58" s="44" t="n"/>
       <c r="BT58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="BU58" s="20" t="n"/>
+      <c r="BU58" s="44" t="n"/>
       <c r="CD58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CE58" s="20" t="n"/>
+      <c r="CE58" s="44" t="n"/>
       <c r="CN58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CO58" s="20" t="n"/>
+      <c r="CO58" s="44" t="n"/>
       <c r="CX58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="CY58" s="20" t="n"/>
+      <c r="CY58" s="44" t="n"/>
       <c r="DH58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="DI58" s="20" t="n"/>
+      <c r="DI58" s="44" t="n"/>
       <c r="DR58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="DS58" s="20" t="n"/>
+      <c r="DS58" s="44" t="n"/>
       <c r="EB58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EC58" s="20" t="n"/>
+      <c r="EC58" s="44" t="n"/>
       <c r="EL58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EM58" s="20" t="n"/>
+      <c r="EM58" s="44" t="n"/>
       <c r="EV58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="EW58" s="20" t="n"/>
+      <c r="EW58" s="44" t="n"/>
       <c r="FF58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="FG58" s="20" t="n"/>
+      <c r="FG58" s="44" t="n"/>
       <c r="FP58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="FQ58" s="20" t="n"/>
+      <c r="FQ58" s="44" t="n"/>
       <c r="FZ58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GA58" s="20" t="n"/>
+      <c r="GA58" s="44" t="n"/>
       <c r="GJ58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GK58" s="20" t="n"/>
+      <c r="GK58" s="44" t="n"/>
       <c r="GT58" s="32" t="inlineStr">
         <is>
           <t>欠席</t>
         </is>
       </c>
-      <c r="GU58" s="20" t="n"/>
+      <c r="GU58" s="44" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="C59" s="33" t="n"/>
-      <c r="M59" s="33" t="n"/>
-      <c r="W59" s="33" t="n"/>
-      <c r="AG59" s="33" t="n"/>
-      <c r="AQ59" s="33" t="n"/>
-      <c r="BA59" s="33" t="n"/>
-      <c r="BK59" s="33" t="n"/>
-      <c r="BU59" s="33" t="n"/>
-      <c r="CE59" s="33" t="n"/>
-      <c r="CO59" s="33" t="n"/>
-      <c r="CY59" s="33" t="n"/>
-      <c r="DI59" s="33" t="n"/>
-      <c r="DS59" s="33" t="n"/>
-      <c r="EC59" s="33" t="n"/>
-      <c r="EM59" s="33" t="n"/>
-      <c r="EW59" s="33" t="n"/>
-      <c r="FG59" s="33" t="n"/>
-      <c r="FQ59" s="33" t="n"/>
-      <c r="GA59" s="33" t="n"/>
-      <c r="GK59" s="33" t="n"/>
-      <c r="GU59" s="33" t="n"/>
+      <c r="C59" s="49" t="n"/>
+      <c r="M59" s="49" t="n"/>
+      <c r="W59" s="49" t="n"/>
+      <c r="AG59" s="49" t="n"/>
+      <c r="AQ59" s="49" t="n"/>
+      <c r="BA59" s="49" t="n"/>
+      <c r="BK59" s="49" t="n"/>
+      <c r="BU59" s="49" t="n"/>
+      <c r="CE59" s="49" t="n"/>
+      <c r="CO59" s="49" t="n"/>
+      <c r="CY59" s="49" t="n"/>
+      <c r="DI59" s="49" t="n"/>
+      <c r="DS59" s="49" t="n"/>
+      <c r="EC59" s="49" t="n"/>
+      <c r="EM59" s="49" t="n"/>
+      <c r="EW59" s="49" t="n"/>
+      <c r="FG59" s="49" t="n"/>
+      <c r="FQ59" s="49" t="n"/>
+      <c r="GA59" s="49" t="n"/>
+      <c r="GK59" s="49" t="n"/>
+      <c r="GU59" s="49" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1">
-      <c r="B60" s="34" t="inlineStr">
+      <c r="B60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="H60" s="35" t="n"/>
-      <c r="I60" s="36" t="n"/>
-      <c r="L60" s="34" t="inlineStr">
+      <c r="H60" s="51" t="n"/>
+      <c r="I60" s="52" t="n"/>
+      <c r="L60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="R60" s="35" t="n"/>
-      <c r="S60" s="36" t="n"/>
-      <c r="V60" s="34" t="inlineStr">
+      <c r="R60" s="51" t="n"/>
+      <c r="S60" s="52" t="n"/>
+      <c r="V60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AB60" s="35" t="n"/>
-      <c r="AC60" s="36" t="n"/>
-      <c r="AF60" s="34" t="inlineStr">
+      <c r="AB60" s="51" t="n"/>
+      <c r="AC60" s="52" t="n"/>
+      <c r="AF60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AL60" s="35" t="n"/>
-      <c r="AM60" s="36" t="n"/>
-      <c r="AP60" s="34" t="inlineStr">
+      <c r="AL60" s="51" t="n"/>
+      <c r="AM60" s="52" t="n"/>
+      <c r="AP60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="AV60" s="35" t="n"/>
-      <c r="AW60" s="36" t="n"/>
-      <c r="AZ60" s="34" t="inlineStr">
+      <c r="AV60" s="51" t="n"/>
+      <c r="AW60" s="52" t="n"/>
+      <c r="AZ60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BF60" s="35" t="n"/>
-      <c r="BG60" s="36" t="n"/>
-      <c r="BJ60" s="34" t="inlineStr">
+      <c r="BF60" s="51" t="n"/>
+      <c r="BG60" s="52" t="n"/>
+      <c r="BJ60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BP60" s="35" t="n"/>
-      <c r="BQ60" s="36" t="n"/>
-      <c r="BT60" s="34" t="inlineStr">
+      <c r="BP60" s="51" t="n"/>
+      <c r="BQ60" s="52" t="n"/>
+      <c r="BT60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="BZ60" s="35" t="n"/>
-      <c r="CA60" s="36" t="n"/>
-      <c r="CD60" s="34" t="inlineStr">
+      <c r="BZ60" s="51" t="n"/>
+      <c r="CA60" s="52" t="n"/>
+      <c r="CD60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="CJ60" s="35" t="n"/>
-      <c r="CK60" s="36" t="n"/>
-      <c r="CN60" s="34" t="inlineStr">
+      <c r="CJ60" s="51" t="n"/>
+      <c r="CK60" s="52" t="n"/>
+      <c r="CN60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="CT60" s="35" t="n"/>
-      <c r="CU60" s="36" t="n"/>
-      <c r="CX60" s="34" t="inlineStr">
+      <c r="CT60" s="51" t="n"/>
+      <c r="CU60" s="52" t="n"/>
+      <c r="CX60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DD60" s="35" t="n"/>
-      <c r="DE60" s="36" t="n"/>
-      <c r="DH60" s="34" t="inlineStr">
+      <c r="DD60" s="51" t="n"/>
+      <c r="DE60" s="52" t="n"/>
+      <c r="DH60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DN60" s="35" t="n"/>
-      <c r="DO60" s="36" t="n"/>
-      <c r="DR60" s="34" t="inlineStr">
+      <c r="DN60" s="51" t="n"/>
+      <c r="DO60" s="52" t="n"/>
+      <c r="DR60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="DX60" s="35" t="n"/>
-      <c r="DY60" s="36" t="n"/>
-      <c r="EB60" s="34" t="inlineStr">
+      <c r="DX60" s="51" t="n"/>
+      <c r="DY60" s="52" t="n"/>
+      <c r="EB60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="EH60" s="35" t="n"/>
-      <c r="EI60" s="36" t="n"/>
-      <c r="EL60" s="34" t="inlineStr">
+      <c r="EH60" s="51" t="n"/>
+      <c r="EI60" s="52" t="n"/>
+      <c r="EL60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="ER60" s="35" t="n"/>
-      <c r="ES60" s="36" t="n"/>
-      <c r="EV60" s="34" t="inlineStr">
+      <c r="ER60" s="51" t="n"/>
+      <c r="ES60" s="52" t="n"/>
+      <c r="EV60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FB60" s="35" t="n"/>
-      <c r="FC60" s="36" t="n"/>
-      <c r="FF60" s="34" t="inlineStr">
+      <c r="FB60" s="51" t="n"/>
+      <c r="FC60" s="52" t="n"/>
+      <c r="FF60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FL60" s="35" t="n"/>
-      <c r="FM60" s="36" t="n"/>
-      <c r="FP60" s="34" t="inlineStr">
+      <c r="FL60" s="51" t="n"/>
+      <c r="FM60" s="52" t="n"/>
+      <c r="FP60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="FV60" s="35" t="n"/>
-      <c r="FW60" s="36" t="n"/>
-      <c r="FZ60" s="34" t="inlineStr">
+      <c r="FV60" s="51" t="n"/>
+      <c r="FW60" s="52" t="n"/>
+      <c r="FZ60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GF60" s="35" t="n"/>
-      <c r="GG60" s="36" t="n"/>
-      <c r="GJ60" s="34" t="inlineStr">
+      <c r="GF60" s="51" t="n"/>
+      <c r="GG60" s="52" t="n"/>
+      <c r="GJ60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GP60" s="35" t="n"/>
-      <c r="GQ60" s="36" t="n"/>
-      <c r="GT60" s="34" t="inlineStr">
+      <c r="GP60" s="51" t="n"/>
+      <c r="GQ60" s="52" t="n"/>
+      <c r="GT60" s="50" t="inlineStr">
         <is>
           <t>カリキュラム進捗</t>
         </is>
       </c>
-      <c r="GZ60" s="35" t="n"/>
-      <c r="HA60" s="36" t="n"/>
+      <c r="GZ60" s="51" t="n"/>
+      <c r="HA60" s="52" t="n"/>
     </row>
     <row r="61" ht="12" customHeight="1">
       <c r="B61" s="37" t="inlineStr">
@@ -8440,127 +8443,127 @@
           <t>備考</t>
         </is>
       </c>
-      <c r="C61" s="38" t="n"/>
+      <c r="C61" s="53" t="n"/>
       <c r="L61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="M61" s="38" t="n"/>
+      <c r="M61" s="53" t="n"/>
       <c r="V61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="W61" s="38" t="n"/>
+      <c r="W61" s="53" t="n"/>
       <c r="AF61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="AG61" s="38" t="n"/>
+      <c r="AG61" s="53" t="n"/>
       <c r="AP61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="AQ61" s="38" t="n"/>
+      <c r="AQ61" s="53" t="n"/>
       <c r="AZ61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BA61" s="38" t="n"/>
+      <c r="BA61" s="53" t="n"/>
       <c r="BJ61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BK61" s="38" t="n"/>
+      <c r="BK61" s="53" t="n"/>
       <c r="BT61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="BU61" s="38" t="n"/>
+      <c r="BU61" s="53" t="n"/>
       <c r="CD61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CE61" s="38" t="n"/>
+      <c r="CE61" s="53" t="n"/>
       <c r="CN61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CO61" s="38" t="n"/>
+      <c r="CO61" s="53" t="n"/>
       <c r="CX61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="CY61" s="38" t="n"/>
+      <c r="CY61" s="53" t="n"/>
       <c r="DH61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="DI61" s="38" t="n"/>
+      <c r="DI61" s="53" t="n"/>
       <c r="DR61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="DS61" s="38" t="n"/>
+      <c r="DS61" s="53" t="n"/>
       <c r="EB61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EC61" s="38" t="n"/>
+      <c r="EC61" s="53" t="n"/>
       <c r="EL61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EM61" s="38" t="n"/>
+      <c r="EM61" s="53" t="n"/>
       <c r="EV61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="EW61" s="38" t="n"/>
+      <c r="EW61" s="53" t="n"/>
       <c r="FF61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="FG61" s="38" t="n"/>
+      <c r="FG61" s="53" t="n"/>
       <c r="FP61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="FQ61" s="38" t="n"/>
+      <c r="FQ61" s="53" t="n"/>
       <c r="FZ61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GA61" s="38" t="n"/>
+      <c r="GA61" s="53" t="n"/>
       <c r="GJ61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GK61" s="38" t="n"/>
+      <c r="GK61" s="53" t="n"/>
       <c r="GT61" s="37" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="GU61" s="38" t="n"/>
+      <c r="GU61" s="53" t="n"/>
     </row>
     <row r="62" ht="12" customHeight="1"/>
     <row r="63" ht="12" customHeight="1"/>
@@ -12635,6 +12638,44 @@
     <mergeCell ref="AP41:AP44"/>
     <mergeCell ref="C18:J18"/>
   </mergeCells>
+  <dataValidations xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12">
+    <dataValidation type="list" sqref="B32 L32 V32 AF32 AP32 AZ32 BJ32 BT32 CD32 CN32 CX32 DH32 DR32 EB32 EL32 EV32 FF32 FP32 FZ32 GJ32 GT32 B72 L72 V72 AF72 AP72 AZ72 BJ72 BT72 CD72 CN72 CX72 DH72 DR72 EB72 EL72 EV72 FF72 FP72 FZ72 GJ72 GT72 B12 L12 V12 AF12 AP12 AZ12 BJ12 BT12 CD12 CN12 CX12 DH12 DR12 EB12 EL12 EV12 FF12 FP12 FZ12 GJ12 GT12 B52 L52 V52 AF52 AP52 AZ52 BJ52 BT52 CD52 CN52 CX52 DH52 DR52 EB52 EL52 EV52 FF52 FP52 FZ52 GJ52 GT52" showDropDown="0" allowBlank="1">
+      <formula1>"×,月,火,水,木,金,土,日"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B51 L51 V51 AF51 AP51 AZ51 BJ51 BT51 CD51 CN51 CX51 DH51 DR51 EB51 EL51 EV51 FF51 FP51 FZ51 GJ51 GT51 B31 L31 V31 AF31 AP31 AZ31 BJ31 BT31 CD31 CN31 CX31 DH31 DR31 EB31 EL31 EV31 FF31 FP31 FZ31 GJ31 GT31 B71 L71 V71 AF71 AP71 AZ71 BJ71 BT71 CD71 CN71 CX71 DH71 DR71 EB71 EL71 EV71 FF71 FP71 FZ71 GJ71 GT71 B11 L11 V11 AF11 AP11 AZ11 BJ11 BT11 CD11 CN11 CX11 DH11 DR11 EB11 EL11 EV11 FF11 FP11 FZ11 GJ11 GT11" showDropDown="0" allowBlank="1">
+      <formula1>"×,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B30 L30 V30 AF30 AP30 AZ30 BJ30 BT30 CD30 CN30 CX30 DH30 DR30 EB30 EL30 EV30 FF30 FP30 FZ30 GJ30 GT30 B50 L50 V50 AF50 AP50 AZ50 BJ50 BT50 CD50 CN50 CX50 DH50 DR50 EB50 EL50 EV50 FF50 FP50 FZ50 GJ50 GT50 B70 L70 V70 AF70 AP70 AZ70 BJ70 BT70 CD70 CN70 CX70 DH70 DR70 EB70 EL70 EV70 FF70 FP70 FZ70 GJ70 GT70 B10 L10 V10 AF10 AP10 AZ10 BJ10 BT10 CD10 CN10 CX10 DH10 DR10 EB10 EL10 EV10 FF10 FP10 FZ10 GJ10 GT10" showDropDown="0" allowBlank="1">
+      <formula1>"×,1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="G3 Q3 AA3 AK3 AU3 BE3 BO3 BY3 CI3 CS3 DC3 DM3 DW3 EG3 EQ3 FA3 FK3 FU3 GE3 GO3 GY3" showDropDown="0" allowBlank="1">
+      <formula1>"特,1,2,3,4,5,6,7,8,9,10"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="F2 G2 P2 Q2 Z2 AA2 AJ2 AK2 AT2 AU2 BD2 BE2 BN2 BO2 BX2 BY2 CH2 CI2 CR2 CS2 DB2 DC2 DL2 DM2 DV2 DW2 EF2 EG2 EP2 EQ2 EZ2 FA2 FJ2 FK2 FT2 FU2 GD2 GE2 GN2 GO2 GX2 GY2" showDropDown="0" allowBlank="1">
+      <formula1>"特,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B2 C2 D2 B3 C3 D3" showDropDown="0" allowBlank="1">
+      <formula1>"本校,南教室"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E3" showDropDown="0" allowBlank="1">
+      <formula1>"1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I2" showDropDown="0" allowBlank="1">
+      <formula1>"1,2,3,4,5,6"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I3 J3" showDropDown="0" allowBlank="1">
+      <formula1>"英語,数学,国語,理科,社会,算数"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B7 C7 B8 C8 L7 M7 L8 M8 V7 W7 V8 W8 AF7 AG7 AF8 AG8 AP7 AQ7 AP8 AQ8 AZ7 BA7 AZ8 BA8 BJ7 BK7 BJ8 BK8 BT7 BU7 BT8 BU8 CD7 CE7 CD8 CE8 CN7 CO7 CN8 CO8 CX7 CY7 CX8 CY8 DH7 DI7 DH8 DI8 DR7 DS7 DR8 DS8 EB7 EC7 EB8 EC8 EL7 EM7 EL8 EM8 EV7 EW7 EV8 EW8 FF7 FG7 FF8 FG8 FP7 FQ7 FP8 FQ8 FZ7 GA7 FZ8 GA8 GJ7 GK7 GJ8 GK8 GT7 GU7 GT8 GU8 B27 C27 B28 C28 L27 M27 L28 M28 V27 W27 V28 W28 AF27 AG27 AF28 AG28 AP27 AQ27 AP28 AQ28 AZ27 BA27 AZ28 BA28 BJ27 BK27 BJ28 BK28 BT27 BU27 BT28 BU28 CD27 CE27 CD28 CE28 CN27 CO27 CN28 CO28 CX27 CY27 CX28 CY28 DH27 DI27 DH28 DI28 DR27 DS27 DR28 DS28 EB27 EC27 EB28 EC28 EL27 EM27 EL28 EM28 EV27 EW27 EV28 EW28 FF27 FG27 FF28 FG28 FP27 FQ27 FP28 FQ28 FZ27 GA27 FZ28 GA28 GJ27 GK27 GJ28 GK28 GT27 GU27 GT28 GU28 B47 C47 B48 C48 L47 M47 L48 M48 V47 W47 V48 W48 AF47 AG47 AF48 AG48 AP47 AQ47 AP48 AQ48 AZ47 BA47 AZ48 BA48 BJ47 BK47 BJ48 BK48 BT47 BU47 BT48 BU48 CD47 CE47 CD48 CE48 CN47 CO47 CN48 CO48 CX47 CY47 CX48 CY48 DH47 DI47 DH48 DI48 DR47 DS47 DR48 DS48 EB47 EC47 EB48 EC48 EL47 EM47 EL48 EM48 EV47 EW47 EV48 EW48 FF47 FG47 FF48 FG48 FP47 FQ47 FP48 FQ48 FZ47 GA47 FZ48 GA48 GJ47 GK47 GJ48 GK48 GT47 GU47 GT48 GU48 B67 C67 B68 C68 L67 M67 L68 M68 V67 W67 V68 W68 AF67 AG67 AF68 AG68 AP67 AQ67 AP68 AQ68 AZ67 BA67 AZ68 BA68 BJ67 BK67 BJ68 BK68 BT67 BU67 BT68 BU68 CD67 CE67 CD68 CE68 CN67 CO67 CN68 CO68 CX67 CY67 CX68 CY68 DH67 DI67 DH68 DI68 DR67 DS67 DR68 DS68 EB67 EC67 EB68 EC68 EL67 EM67 EL68 EM68 EV67 EW67 EV68 EW68 FF67 FG67 FF68 FG68 FP67 FQ67 FP68 FQ68 FZ67 GA67 FZ68 GA68 GJ67 GK67 GJ68 GK68 GT67 GU67 GT68 GU68" showDropDown="0" allowBlank="1">
+      <formula1>"Ｓ,Ａ,Ｂ,Ｃ,Ｄ,Ｅ,Ｆ,Ｇ,Ｘ"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H80 R80 AB80 AL80 AV80 BF80 BP80 BZ80 CJ80 CT80 DD80 DN80 DX80 EH80 ER80 FB80 FL80 FV80 GF80 GP80 GZ80 H20 R20 AB20 AL20 AV20 BF20 BP20 BZ20 CJ20 CT20 DD20 DN20 DX20 EH20 ER20 FB20 FL20 FV20 GF20 GP20 GZ20 H40 R40 AB40 AL40 AV40 BF40 BP40 BZ40 CJ40 CT40 DD40 DN40 DX40 EH40 ER40 FB40 FL40 FV40 GF40 GP40 GZ40 H60 R60 AB60 AL60 AV60 BF60 BP60 BZ60 CJ60 CT60 DD60 DN60 DX60 EH60 ER60 FB60 FL60 FV60 GF60 GP60 GZ60" showDropDown="0" allowBlank="1">
+      <formula1>"＋,－,±"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="B34 C34 B35 C35 L34 M34 L35 M35 V34 W34 V35 W35 AF34 AG34 AF35 AG35 AP34 AQ34 AP35 AQ35 AZ34 BA34 AZ35 BA35 BJ34 BK34 BJ35 BK35 BT34 BU34 BT35 BU35 CD34 CE34 CD35 CE35 CN34 CO34 CN35 CO35 CX34 CY34 CX35 CY35 DH34 DI34 DH35 DI35 DR34 DS34 DR35 DS35 EB34 EC34 EB35 EC35 EL34 EM34 EL35 EM35 EV34 EW34 EV35 EW35 FF34 FG34 FF35 FG35 FP34 FQ34 FP35 FQ35 FZ34 GA34 FZ35 GA35 GJ34 GK34 GJ35 GK35 GT34 GU34 GT35 GU35 B74 C74 B75 C75 L74 M74 L75 M75 V74 W74 V75 W75 AF74 AG74 AF75 AG75 AP74 AQ74 AP75 AQ75 AZ74 BA74 AZ75 BA75 BJ74 BK74 BJ75 BK75 BT74 BU74 BT75 BU75 CD74 CE74 CD75 CE75 CN74 CO74 CN75 CO75 CX74 CY74 CX75 CY75 DH74 DI74 DH75 DI75 DR74 DS74 DR75 DS75 EB74 EC74 EB75 EC75 EL74 EM74 EL75 EM75 EV74 EW74 EV75 EW75 FF74 FG74 FF75 FG75 FP74 FQ74 FP75 FQ75 FZ74 GA74 FZ75 GA75 GJ74 GK74 GJ75 GK75 GT74 GU74 GT75 GU75 B54 C54 B55 C55 L54 M54 L55 M55 V54 W54 V55 W55 AF54 AG54 AF55 AG55 AP54 AQ54 AP55 AQ55 AZ54 BA54 AZ55 BA55 BJ54 BK54 BJ55 BK55 BT54 BU54 BT55 BU55 CD54 CE54 CD55 CE55 CN54 CO54 CN55 CO55 CX54 CY54 CX55 CY55 DH54 DI54 DH55 DI55 DR54 DS54 DR55 DS55 EB54 EC54 EB55 EC55 EL54 EM54 EL55 EM55 EV54 EW54 EV55 EW55 FF54 FG54 FF55 FG55 FP54 FQ54 FP55 FQ55 FZ54 GA54 FZ55 GA55 GJ54 GK54 GJ55 GK55 GT54 GU54 GT55 GU55 B14 C14 B15 C15 L14 M14 L15 M15 V14 W14 V15 W15 AF14 AG14 AF15 AG15 AP14 AQ14 AP15 AQ15 AZ14 BA14 AZ15 BA15 BJ14 BK14 BJ15 BK15 BT14 BU14 BT15 BU15 CD14 CE14 CD15 CE15 CN14 CO14 CN15 CO15 CX14 CY14 CX15 CY15 DH14 DI14 DH15 DI15 DR14 DS14 DR15 DS15 EB14 EC14 EB15 EC15 EL14 EM14 EL15 EM15 EV14 EW14 EV15 EW15 FF14 FG14 FF15 FG15 FP14 FQ14 FP15 FQ15 FZ14 GA14 FZ15 GA15 GJ14 GK14 GJ15 GK15 GT14 GU14 GT15 GU15" showDropDown="0" allowBlank="1">
+      <formula1>"塾長,文章,金城,鈴木,石川,高山,佐藤,金子,吉田,工藤,真下,岩本,染谷"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/scripts/TEMPLATE_MAIN.xlsx
+++ b/scripts/TEMPLATE_MAIN.xlsx
@@ -135,7 +135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61">
     <border>
       <left/>
       <right/>
@@ -551,11 +551,329 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="dotted">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55">
+  <cellXfs xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -746,6 +1064,90 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="54" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="57" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1112,15 +1514,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HC84"/>
+  <dimension xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:HD84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
+  <cols xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
     <col width="3.42578125" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
-    <col width="3.42578125" customWidth="1" min="212" max="212"/>
     <col width="3.42578125" customWidth="1" min="213" max="213"/>
+    <col hidden="1" width="3.42578125" customWidth="1" min="212" max="212"/>
   </cols>
   <sheetData>
     <row r="1" ht="9.949999999999999" customHeight="1"/>
@@ -1164,7 +1566,7 @@
         </is>
       </c>
       <c r="P2" s="3">
-        <f>IF(F2="","",IF(F2="特",IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)),F2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(F2="","",IF(F2="特",IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)),F2+1))</f>
         <v/>
       </c>
       <c r="R2" s="4" t="inlineStr">
@@ -1193,7 +1595,7 @@
         </is>
       </c>
       <c r="Z2" s="3">
-        <f>IF(P2="","",IF(P2="特",IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))),P2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(P2="","",IF(P2="特",IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))),P2+1))</f>
         <v/>
       </c>
       <c r="AB2" s="4" t="inlineStr">
@@ -1222,7 +1624,7 @@
         </is>
       </c>
       <c r="AJ2" s="3">
-        <f>IF(Z2="","",IF(Z2="特",IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))),Z2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(Z2="","",IF(Z2="特",IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))),Z2+1))</f>
         <v/>
       </c>
       <c r="AL2" s="4" t="inlineStr">
@@ -1251,7 +1653,7 @@
         </is>
       </c>
       <c r="AT2" s="3">
-        <f>IF(AJ2="","",IF(AJ2="特",IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))),AJ2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(AJ2="","",IF(AJ2="特",IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))),AJ2+1))</f>
         <v/>
       </c>
       <c r="AV2" s="4" t="inlineStr">
@@ -1280,7 +1682,7 @@
         </is>
       </c>
       <c r="BD2" s="3">
-        <f>IF(AT2="","",IF(AT2="特",IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))),AT2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(AT2="","",IF(AT2="特",IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))),AT2+1))</f>
         <v/>
       </c>
       <c r="BF2" s="4" t="inlineStr">
@@ -1309,7 +1711,7 @@
         </is>
       </c>
       <c r="BN2" s="3">
-        <f>IF(BD2="","",IF(BD2="特",IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))),BD2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(BD2="","",IF(BD2="特",IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))),BD2+1))</f>
         <v/>
       </c>
       <c r="BP2" s="4" t="inlineStr">
@@ -1338,7 +1740,7 @@
         </is>
       </c>
       <c r="BX2" s="3">
-        <f>IF(BN2="","",IF(BN2="特",IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))))),BN2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(BN2="","",IF(BN2="特",IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))))),BN2+1))</f>
         <v/>
       </c>
       <c r="BZ2" s="4" t="inlineStr">
@@ -1367,7 +1769,7 @@
         </is>
       </c>
       <c r="CH2" s="3">
-        <f>IF(BX2="","",IF(BX2="特",IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))))),BX2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(BX2="","",IF(BX2="特",IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))))),BX2+1))</f>
         <v/>
       </c>
       <c r="CJ2" s="4" t="inlineStr">
@@ -1396,7 +1798,7 @@
         </is>
       </c>
       <c r="CR2" s="3">
-        <f>IF(CH2="","",IF(CH2="特",IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))))))),CH2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(CH2="","",IF(CH2="特",IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))))))),CH2+1))</f>
         <v/>
       </c>
       <c r="CT2" s="4" t="inlineStr">
@@ -1425,7 +1827,7 @@
         </is>
       </c>
       <c r="DB2" s="3">
-        <f>IF(CR2="","",IF(CR2="特",IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))))))),CR2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(CR2="","",IF(CR2="特",IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))))))),CR2+1))</f>
         <v/>
       </c>
       <c r="DD2" s="4" t="inlineStr">
@@ -1454,7 +1856,7 @@
         </is>
       </c>
       <c r="DL2" s="3">
-        <f>IF(DB2="","",IF(DB2="特",IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))))))))),DB2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(DB2="","",IF(DB2="特",IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))))))))),DB2+1))</f>
         <v/>
       </c>
       <c r="DN2" s="4" t="inlineStr">
@@ -1483,7 +1885,7 @@
         </is>
       </c>
       <c r="DV2" s="3">
-        <f>IF(DL2="","",IF(DL2="特",IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))))))))),DL2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(DL2="","",IF(DL2="特",IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))))))))),DL2+1))</f>
         <v/>
       </c>
       <c r="DX2" s="4" t="inlineStr">
@@ -1512,7 +1914,7 @@
         </is>
       </c>
       <c r="EF2" s="3">
-        <f>IF(DV2="","",IF(DV2="特",IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))))))))))),DV2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(DV2="","",IF(DV2="特",IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))))))))))),DV2+1))</f>
         <v/>
       </c>
       <c r="EH2" s="4" t="inlineStr">
@@ -1541,7 +1943,7 @@
         </is>
       </c>
       <c r="EP2" s="3">
-        <f>IF(EF2="","",IF(EF2="特",IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))))))))))),EF2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(EF2="","",IF(EF2="特",IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))))))))))),EF2+1))</f>
         <v/>
       </c>
       <c r="ER2" s="4" t="inlineStr">
@@ -1570,7 +1972,7 @@
         </is>
       </c>
       <c r="EZ2" s="3">
-        <f>IF(EP2="","",IF(EP2="特",IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))))))))))))),EP2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(EP2="","",IF(EP2="特",IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))))))))))))),EP2+1))</f>
         <v/>
       </c>
       <c r="FB2" s="4" t="inlineStr">
@@ -1599,7 +2001,7 @@
         </is>
       </c>
       <c r="FJ2" s="3">
-        <f>IF(EZ2="","",IF(EZ2="特",IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))))))))))))),EZ2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(EZ2="","",IF(EZ2="特",IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))))))))))))),EZ2+1))</f>
         <v/>
       </c>
       <c r="FL2" s="4" t="inlineStr">
@@ -1628,7 +2030,7 @@
         </is>
       </c>
       <c r="FT2" s="3">
-        <f>IF(FJ2="","",IF(FJ2="特",IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))))))))))))))),FJ2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(FJ2="","",IF(FJ2="特",IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))))))))))))))),FJ2+1))</f>
         <v/>
       </c>
       <c r="FV2" s="4" t="inlineStr">
@@ -1657,7 +2059,7 @@
         </is>
       </c>
       <c r="GD2" s="3">
-        <f>IF(FT2="","",IF(FT2="特",IF(ISNUMBER(FT2),FT2+1,IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))))))))))))))),FT2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(FT2="","",IF(FT2="特",IF(ISNUMBER(FT2),FT2+1,IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))))))))))))))),FT2+1))</f>
         <v/>
       </c>
       <c r="GF2" s="4" t="inlineStr">
@@ -1686,7 +2088,7 @@
         </is>
       </c>
       <c r="GN2" s="3">
-        <f>IF(GD2="","",IF(GD2="特",IF(ISNUMBER(GD2),GD2+1,IF(ISNUMBER(FT2),FT2+1,IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2)))))))))))))))))))),GD2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(GD2="","",IF(GD2="特",IF(ISNUMBER(GD2),GD2+1,IF(ISNUMBER(FT2),FT2+1,IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2)))))))))))))))))))),GD2+1))</f>
         <v/>
       </c>
       <c r="GP2" s="4" t="inlineStr">
@@ -1715,7 +2117,7 @@
         </is>
       </c>
       <c r="GX2" s="3">
-        <f>IF(GN2="","",IF(GN2="特",IF(ISNUMBER(GN2),GN2+1,IF(ISNUMBER(GD2),GD2+1,IF(ISNUMBER(FT2),FT2+1,IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($FG$2="","",$FG$2))))))))))))))))))))),GN2+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(GN2="","",IF(GN2="特",IF(ISNUMBER(GN2),GN2+1,IF(ISNUMBER(GD2),GD2+1,IF(ISNUMBER(FT2),FT2+1,IF(ISNUMBER(FJ2),FJ2+1,IF(ISNUMBER(EZ2),EZ2+1,IF(ISNUMBER(EP2),EP2+1,IF(ISNUMBER(EF2),EF2+1,IF(ISNUMBER(DV2),DV2+1,IF(ISNUMBER(DL2),DL2+1,IF(ISNUMBER(DB2),DB2+1,IF(ISNUMBER(CR2),CR2+1,IF(ISNUMBER(CH2),CH2+1,IF(ISNUMBER(BX2),BX2+1,IF(ISNUMBER(BN2),BN2+1,IF(ISNUMBER(BD2),BD2+1,IF(ISNUMBER(AT2),AT2+1,IF(ISNUMBER(AJ2),AJ2+1,IF(ISNUMBER(Z2),Z2+1,IF(ISNUMBER(P2),P2+1,IF(ISNUMBER(F2),F2+1,IF($HD$2="","",$HD$2))))))))))))))))))))),GN2+1))</f>
         <v/>
       </c>
       <c r="GZ2" s="4" t="inlineStr">
@@ -1732,6 +2134,9 @@
         <is>
           <t>年</t>
         </is>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="HD2" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1">
@@ -1765,7 +2170,7 @@
         </is>
       </c>
       <c r="Q3" s="8">
-        <f>IF(G3="","",IF(G3="特",IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)),G3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(G3="","",IF(G3="特",IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)),G3+1))</f>
         <v/>
       </c>
       <c r="R3" s="9" t="inlineStr">
@@ -1787,7 +2192,7 @@
         </is>
       </c>
       <c r="AA3" s="8">
-        <f>IF(Q3="","",IF(Q3="特",IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))),Q3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(Q3="","",IF(Q3="特",IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))),Q3+1))</f>
         <v/>
       </c>
       <c r="AB3" s="9" t="inlineStr">
@@ -1809,7 +2214,7 @@
         </is>
       </c>
       <c r="AK3" s="8">
-        <f>IF(AA3="","",IF(AA3="特",IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))),AA3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(AA3="","",IF(AA3="特",IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))),AA3+1))</f>
         <v/>
       </c>
       <c r="AL3" s="9" t="inlineStr">
@@ -1831,7 +2236,7 @@
         </is>
       </c>
       <c r="AU3" s="8">
-        <f>IF(AK3="","",IF(AK3="特",IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))),AK3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(AK3="","",IF(AK3="特",IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))),AK3+1))</f>
         <v/>
       </c>
       <c r="AV3" s="9" t="inlineStr">
@@ -1853,7 +2258,7 @@
         </is>
       </c>
       <c r="BE3" s="8">
-        <f>IF(AU3="","",IF(AU3="特",IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))),AU3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(AU3="","",IF(AU3="特",IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))),AU3+1))</f>
         <v/>
       </c>
       <c r="BF3" s="9" t="inlineStr">
@@ -1875,7 +2280,7 @@
         </is>
       </c>
       <c r="BO3" s="8">
-        <f>IF(BE3="","",IF(BE3="特",IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))),BE3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(BE3="","",IF(BE3="特",IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))),BE3+1))</f>
         <v/>
       </c>
       <c r="BP3" s="9" t="inlineStr">
@@ -1897,7 +2302,7 @@
         </is>
       </c>
       <c r="BY3" s="8">
-        <f>IF(BO3="","",IF(BO3="特",IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))))),BO3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(BO3="","",IF(BO3="特",IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))))),BO3+1))</f>
         <v/>
       </c>
       <c r="BZ3" s="9" t="inlineStr">
@@ -1919,7 +2324,7 @@
         </is>
       </c>
       <c r="CI3" s="8">
-        <f>IF(BY3="","",IF(BY3="特",IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))))),BY3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(BY3="","",IF(BY3="特",IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))))),BY3+1))</f>
         <v/>
       </c>
       <c r="CJ3" s="9" t="inlineStr">
@@ -1941,7 +2346,7 @@
         </is>
       </c>
       <c r="CS3" s="8">
-        <f>IF(CI3="","",IF(CI3="特",IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))))))),CI3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(CI3="","",IF(CI3="特",IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))))))),CI3+1))</f>
         <v/>
       </c>
       <c r="CT3" s="9" t="inlineStr">
@@ -1963,7 +2368,7 @@
         </is>
       </c>
       <c r="DC3" s="8">
-        <f>IF(CS3="","",IF(CS3="特",IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))))))),CS3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(CS3="","",IF(CS3="特",IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))))))),CS3+1))</f>
         <v/>
       </c>
       <c r="DD3" s="9" t="inlineStr">
@@ -1985,7 +2390,7 @@
         </is>
       </c>
       <c r="DM3" s="8">
-        <f>IF(DC3="","",IF(DC3="特",IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))))))))),DC3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(DC3="","",IF(DC3="特",IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))))))))),DC3+1))</f>
         <v/>
       </c>
       <c r="DN3" s="9" t="inlineStr">
@@ -2007,7 +2412,7 @@
         </is>
       </c>
       <c r="DW3" s="8">
-        <f>IF(DM3="","",IF(DM3="特",IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))))))))),DM3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(DM3="","",IF(DM3="特",IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))))))))),DM3+1))</f>
         <v/>
       </c>
       <c r="DX3" s="9" t="inlineStr">
@@ -2029,7 +2434,7 @@
         </is>
       </c>
       <c r="EG3" s="8">
-        <f>IF(DW3="","",IF(DW3="特",IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))))))))))),DW3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(DW3="","",IF(DW3="特",IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))))))))))),DW3+1))</f>
         <v/>
       </c>
       <c r="EH3" s="9" t="inlineStr">
@@ -2051,7 +2456,7 @@
         </is>
       </c>
       <c r="EQ3" s="8">
-        <f>IF(EG3="","",IF(EG3="特",IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))))))))))),EG3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(EG3="","",IF(EG3="特",IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))))))))))),EG3+1))</f>
         <v/>
       </c>
       <c r="ER3" s="9" t="inlineStr">
@@ -2073,7 +2478,7 @@
         </is>
       </c>
       <c r="FA3" s="8">
-        <f>IF(EQ3="","",IF(EQ3="特",IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))))))))))))),EQ3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(EQ3="","",IF(EQ3="特",IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))))))))))))),EQ3+1))</f>
         <v/>
       </c>
       <c r="FB3" s="9" t="inlineStr">
@@ -2095,7 +2500,7 @@
         </is>
       </c>
       <c r="FK3" s="8">
-        <f>IF(FA3="","",IF(FA3="特",IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))))))))))))),FA3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(FA3="","",IF(FA3="特",IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))))))))))))),FA3+1))</f>
         <v/>
       </c>
       <c r="FL3" s="9" t="inlineStr">
@@ -2117,7 +2522,7 @@
         </is>
       </c>
       <c r="FU3" s="8">
-        <f>IF(FK3="","",IF(FK3="特",IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))))))))))))))),FK3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(FK3="","",IF(FK3="特",IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))))))))))))))),FK3+1))</f>
         <v/>
       </c>
       <c r="FV3" s="9" t="inlineStr">
@@ -2139,7 +2544,7 @@
         </is>
       </c>
       <c r="GE3" s="8">
-        <f>IF(FU3="","",IF(FU3="特",IF(ISNUMBER(FU3),FU3+1,IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))))))))))))))),FU3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(FU3="","",IF(FU3="特",IF(ISNUMBER(FU3),FU3+1,IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))))))))))))))),FU3+1))</f>
         <v/>
       </c>
       <c r="GF3" s="9" t="inlineStr">
@@ -2161,7 +2566,7 @@
         </is>
       </c>
       <c r="GO3" s="8">
-        <f>IF(GE3="","",IF(GE3="特",IF(ISNUMBER(GE3),GE3+1,IF(ISNUMBER(FU3),FU3+1,IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3)))))))))))))))))))),GE3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(GE3="","",IF(GE3="特",IF(ISNUMBER(GE3),GE3+1,IF(ISNUMBER(FU3),FU3+1,IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3)))))))))))))))))))),GE3+1))</f>
         <v/>
       </c>
       <c r="GP3" s="9" t="inlineStr">
@@ -2183,7 +2588,7 @@
         </is>
       </c>
       <c r="GY3" s="8">
-        <f>IF(GO3="","",IF(GO3="特",IF(ISNUMBER(GO3),GO3+1,IF(ISNUMBER(GE3),GE3+1,IF(ISNUMBER(FU3),FU3+1,IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($FG$3="","",$FG$3))))))))))))))))))))),GO3+1))</f>
+        <f xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">IF(GO3="","",IF(GO3="特",IF(ISNUMBER(GO3),GO3+1,IF(ISNUMBER(GE3),GE3+1,IF(ISNUMBER(FU3),FU3+1,IF(ISNUMBER(FK3),FK3+1,IF(ISNUMBER(FA3),FA3+1,IF(ISNUMBER(EQ3),EQ3+1,IF(ISNUMBER(EG3),EG3+1,IF(ISNUMBER(DW3),DW3+1,IF(ISNUMBER(DM3),DM3+1,IF(ISNUMBER(DC3),DC3+1,IF(ISNUMBER(CS3),CS3+1,IF(ISNUMBER(CI3),CI3+1,IF(ISNUMBER(BY3),BY3+1,IF(ISNUMBER(BO3),BO3+1,IF(ISNUMBER(BE3),BE3+1,IF(ISNUMBER(AU3),AU3+1,IF(ISNUMBER(AK3),AK3+1,IF(ISNUMBER(AA3),AA3+1,IF(ISNUMBER(Q3),Q3+1,IF(ISNUMBER(G3),G3+1,IF($HD$3="","",$HD$3))))))))))))))))))))),GO3+1))</f>
         <v/>
       </c>
       <c r="GZ3" s="9" t="inlineStr">
@@ -2195,6 +2600,9 @@
         <is>
           <t>英語</t>
         </is>
+      </c>
+      <c xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" r="HD3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="7.5" customHeight="1"/>
@@ -10557,7 +10965,7 @@
     <row r="83" ht="12" customHeight="1"/>
     <row r="84" ht="12" customHeight="1"/>
   </sheetData>
-  <mergeCells count="2079">
+  <mergeCells xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2079">
     <mergeCell ref="FR17:FX17"/>
     <mergeCell ref="FP73:FQ73"/>
     <mergeCell ref="DR36:DS36"/>
@@ -12639,40 +13047,40 @@
     <mergeCell ref="C18:J18"/>
   </mergeCells>
   <dataValidations xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12">
-    <dataValidation type="list" sqref="B32 L32 V32 AF32 AP32 AZ32 BJ32 BT32 CD32 CN32 CX32 DH32 DR32 EB32 EL32 EV32 FF32 FP32 FZ32 GJ32 GT32 B72 L72 V72 AF72 AP72 AZ72 BJ72 BT72 CD72 CN72 CX72 DH72 DR72 EB72 EL72 EV72 FF72 FP72 FZ72 GJ72 GT72 B12 L12 V12 AF12 AP12 AZ12 BJ12 BT12 CD12 CN12 CX12 DH12 DR12 EB12 EL12 EV12 FF12 FP12 FZ12 GJ12 GT12 B52 L52 V52 AF52 AP52 AZ52 BJ52 BT52 CD52 CN52 CX52 DH52 DR52 EB52 EL52 EV52 FF52 FP52 FZ52 GJ52 GT52" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="B12 B32 B52 B72 L12 L32 L52 L72 V12 V32 V52 V72 AF12 AF32 AF52 AF72 AP12 AP32 AP52 AP72 AZ12 AZ32 AZ52 AZ72 BJ12 BJ32 BJ52 BJ72 BT12 BT32 BT52 BT72 CD12 CD32 CD52 CD72 CN12 CN32 CN52 CN72 CX12 CX32 CX52 CX72 DH12 DH32 DH52 DH72 DR12 DR32 DR52 DR72 EB12 EB32 EB52 EB72 EL12 EL32 EL52 EL72 EV12 EV32 EV52 EV72 FF12 FF32 FF52 FF72 FP12 FP32 FP52 FP72 FZ12 FZ32 FZ52 FZ72 GJ12 GJ32 GJ52 GJ72 GT12 GT32 GT52 GT72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"×,月,火,水,木,金,土,日"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B51 L51 V51 AF51 AP51 AZ51 BJ51 BT51 CD51 CN51 CX51 DH51 DR51 EB51 EL51 EV51 FF51 FP51 FZ51 GJ51 GT51 B31 L31 V31 AF31 AP31 AZ31 BJ31 BT31 CD31 CN31 CX31 DH31 DR31 EB31 EL31 EV31 FF31 FP31 FZ31 GJ31 GT31 B71 L71 V71 AF71 AP71 AZ71 BJ71 BT71 CD71 CN71 CX71 DH71 DR71 EB71 EL71 EV71 FF71 FP71 FZ71 GJ71 GT71 B11 L11 V11 AF11 AP11 AZ11 BJ11 BT11 CD11 CN11 CX11 DH11 DR11 EB11 EL11 EV11 FF11 FP11 FZ11 GJ11 GT11" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="B11 B31 B51 B71 L11 L31 L51 L71 V11 V31 V51 V71 AF11 AF31 AF51 AF71 AP11 AP31 AP51 AP71 AZ11 AZ31 AZ51 AZ71 BJ11 BJ31 BJ51 BJ71 BT11 BT31 BT51 BT71 CD11 CD31 CD51 CD71 CN11 CN31 CN51 CN71 CX11 CX31 CX51 CX71 DH11 DH31 DH51 DH71 DR11 DR31 DR51 DR71 EB11 EB31 EB51 EB71 EL11 EL31 EL51 EL71 EV11 EV31 EV51 EV71 FF11 FF31 FF51 FF71 FP11 FP31 FP51 FP71 FZ11 FZ31 FZ51 FZ71 GJ11 GJ31 GJ51 GJ71 GT11 GT31 GT51 GT71" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"×,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B30 L30 V30 AF30 AP30 AZ30 BJ30 BT30 CD30 CN30 CX30 DH30 DR30 EB30 EL30 EV30 FF30 FP30 FZ30 GJ30 GT30 B50 L50 V50 AF50 AP50 AZ50 BJ50 BT50 CD50 CN50 CX50 DH50 DR50 EB50 EL50 EV50 FF50 FP50 FZ50 GJ50 GT50 B70 L70 V70 AF70 AP70 AZ70 BJ70 BT70 CD70 CN70 CX70 DH70 DR70 EB70 EL70 EV70 FF70 FP70 FZ70 GJ70 GT70 B10 L10 V10 AF10 AP10 AZ10 BJ10 BT10 CD10 CN10 CX10 DH10 DR10 EB10 EL10 EV10 FF10 FP10 FZ10 GJ10 GT10" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="B10 B30 B50 B70 L10 L30 L50 L70 V10 V30 V50 V70 AF10 AF30 AF50 AF70 AP10 AP30 AP50 AP70 AZ10 AZ30 AZ50 AZ70 BJ10 BJ30 BJ50 BJ70 BT10 BT30 BT50 BT70 CD10 CD30 CD50 CD70 CN10 CN30 CN50 CN70 CX10 CX30 CX50 CX70 DH10 DH30 DH50 DH70 DR10 DR30 DR50 DR70 EB10 EB30 EB50 EB70 EL10 EL30 EL50 EL70 EV10 EV30 EV50 EV70 FF10 FF30 FF50 FF70 FP10 FP30 FP50 FP70 FZ10 FZ30 FZ50 FZ70 GJ10 GJ30 GJ50 GJ70 GT10 GT30 GT50 GT70" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"×,1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G3 Q3 AA3 AK3 AU3 BE3 BO3 BY3 CI3 CS3 DC3 DM3 DW3 EG3 EQ3 FA3 FK3 FU3 GE3 GO3 GY3" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="G3 Q3 AA3 AK3 AU3 BE3 BO3 BY3 CI3 CS3 DC3 DM3 DW3 EG3 EQ3 FA3 FK3 FU3 GE3 GO3 GY3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"特,1,2,3,4,5,6,7,8,9,10"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="F2 G2 P2 Q2 Z2 AA2 AJ2 AK2 AT2 AU2 BD2 BE2 BN2 BO2 BX2 BY2 CH2 CI2 CR2 CS2 DB2 DC2 DL2 DM2 DV2 DW2 EF2 EG2 EP2 EQ2 EZ2 FA2 FJ2 FK2 FT2 FU2 GD2 GE2 GN2 GO2 GX2 GY2" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="F2 G2 P2 Q2 Z2 AA2 AJ2 AK2 AT2 AU2 BD2 BE2 BN2 BO2 BX2 BY2 CH2 CI2 CR2 CS2 DB2 DC2 DL2 DM2 DV2 DW2 EF2 EG2 EP2 EQ2 EZ2 FA2 FJ2 FK2 FT2 FU2 GD2 GE2 GN2 GO2 GX2 GY2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"特,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18,19,20,21,22,23,24,25,26,27,28,29,30,31,32,33,34,35,36,37,38,39,40,41,42,43,44,45,46,47,48,49,50,51,52,53,54,55,56,57,58,59,60,61,62,63,64,65,66,67,68,69,70,71,72,73,74,75,76,77,78,79,80"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B2 C2 D2 B3 C3 D3" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="B2 B3 C2 C3 D2 D3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"本校,南教室"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E3" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="E3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5,6,7,8,9,10,11,12"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I2" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="I2" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,3,4,5,6"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I3 J3" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="I3 J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"英語,数学,国語,理科,社会,算数"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B7 C7 B8 C8 L7 M7 L8 M8 V7 W7 V8 W8 AF7 AG7 AF8 AG8 AP7 AQ7 AP8 AQ8 AZ7 BA7 AZ8 BA8 BJ7 BK7 BJ8 BK8 BT7 BU7 BT8 BU8 CD7 CE7 CD8 CE8 CN7 CO7 CN8 CO8 CX7 CY7 CX8 CY8 DH7 DI7 DH8 DI8 DR7 DS7 DR8 DS8 EB7 EC7 EB8 EC8 EL7 EM7 EL8 EM8 EV7 EW7 EV8 EW8 FF7 FG7 FF8 FG8 FP7 FQ7 FP8 FQ8 FZ7 GA7 FZ8 GA8 GJ7 GK7 GJ8 GK8 GT7 GU7 GT8 GU8 B27 C27 B28 C28 L27 M27 L28 M28 V27 W27 V28 W28 AF27 AG27 AF28 AG28 AP27 AQ27 AP28 AQ28 AZ27 BA27 AZ28 BA28 BJ27 BK27 BJ28 BK28 BT27 BU27 BT28 BU28 CD27 CE27 CD28 CE28 CN27 CO27 CN28 CO28 CX27 CY27 CX28 CY28 DH27 DI27 DH28 DI28 DR27 DS27 DR28 DS28 EB27 EC27 EB28 EC28 EL27 EM27 EL28 EM28 EV27 EW27 EV28 EW28 FF27 FG27 FF28 FG28 FP27 FQ27 FP28 FQ28 FZ27 GA27 FZ28 GA28 GJ27 GK27 GJ28 GK28 GT27 GU27 GT28 GU28 B47 C47 B48 C48 L47 M47 L48 M48 V47 W47 V48 W48 AF47 AG47 AF48 AG48 AP47 AQ47 AP48 AQ48 AZ47 BA47 AZ48 BA48 BJ47 BK47 BJ48 BK48 BT47 BU47 BT48 BU48 CD47 CE47 CD48 CE48 CN47 CO47 CN48 CO48 CX47 CY47 CX48 CY48 DH47 DI47 DH48 DI48 DR47 DS47 DR48 DS48 EB47 EC47 EB48 EC48 EL47 EM47 EL48 EM48 EV47 EW47 EV48 EW48 FF47 FG47 FF48 FG48 FP47 FQ47 FP48 FQ48 FZ47 GA47 FZ48 GA48 GJ47 GK47 GJ48 GK48 GT47 GU47 GT48 GU48 B67 C67 B68 C68 L67 M67 L68 M68 V67 W67 V68 W68 AF67 AG67 AF68 AG68 AP67 AQ67 AP68 AQ68 AZ67 BA67 AZ68 BA68 BJ67 BK67 BJ68 BK68 BT67 BU67 BT68 BU68 CD67 CE67 CD68 CE68 CN67 CO67 CN68 CO68 CX67 CY67 CX68 CY68 DH67 DI67 DH68 DI68 DR67 DS67 DR68 DS68 EB67 EC67 EB68 EC68 EL67 EM67 EL68 EM68 EV67 EW67 EV68 EW68 FF67 FG67 FF68 FG68 FP67 FQ67 FP68 FQ68 FZ67 GA67 FZ68 GA68 GJ67 GK67 GJ68 GK68 GT67 GU67 GT68 GU68" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="B7 B8 B27 B28 B47 B48 B67 B68 C7 C8 C27 C28 C47 C48 C67 C68 L7 L8 L27 L28 L47 L48 L67 L68 M7 M8 M27 M28 M47 M48 M67 M68 V7 V8 V27 V28 V47 V48 V67 V68 W7 W8 W27 W28 W47 W48 W67 W68 AF7 AF8 AF27 AF28 AF47 AF48 AF67 AF68 AG7 AG8 AG27 AG28 AG47 AG48 AG67 AG68 AP7 AP8 AP27 AP28 AP47 AP48 AP67 AP68 AQ7 AQ8 AQ27 AQ28 AQ47 AQ48 AQ67 AQ68 AZ7 AZ8 AZ27 AZ28 AZ47 AZ48 AZ67 AZ68 BA7 BA8 BA27 BA28 BA47 BA48 BA67 BA68 BJ7 BJ8 BJ27 BJ28 BJ47 BJ48 BJ67 BJ68 BK7 BK8 BK27 BK28 BK47 BK48 BK67 BK68 BT7 BT8 BT27 BT28 BT47 BT48 BT67 BT68 BU7 BU8 BU27 BU28 BU47 BU48 BU67 BU68 CD7 CD8 CD27 CD28 CD47 CD48 CD67 CD68 CE7 CE8 CE27 CE28 CE47 CE48 CE67 CE68 CN7 CN8 CN27 CN28 CN47 CN48 CN67 CN68 CO7 CO8 CO27 CO28 CO47 CO48 CO67 CO68 CX7 CX8 CX27 CX28 CX47 CX48 CX67 CX68 CY7 CY8 CY27 CY28 CY47 CY48 CY67 CY68 DH7 DH8 DH27 DH28 DH47 DH48 DH67 DH68 DI7 DI8 DI27 DI28 DI47 DI48 DI67 DI68 DR7 DR8 DR27 DR28 DR47 DR48 DR67 DR68 DS7 DS8 DS27 DS28 DS47 DS48 DS67 DS68 EB7 EB8 EB27 EB28 EB47 EB48 EB67 EB68 EC7 EC8 EC27 EC28 EC47 EC48 EC67 EC68 EL7 EL8 EL27 EL28 EL47 EL48 EL67 EL68 EM7 EM8 EM27 EM28 EM47 EM48 EM67 EM68 EV7 EV8 EV27 EV28 EV47 EV48 EV67 EV68 EW7 EW8 EW27 EW28 EW47 EW48 EW67 EW68 FF7 FF8 FF27 FF28 FF47 FF48 FF67 FF68 FG7 FG8 FG27 FG28 FG47 FG48 FG67 FG68 FP7 FP8 FP27 FP28 FP47 FP48 FP67 FP68 FQ7 FQ8 FQ27 FQ28 FQ47 FQ48 FQ67 FQ68 FZ7 FZ8 FZ27 FZ28 FZ47 FZ48 FZ67 FZ68 GA7 GA8 GA27 GA28 GA47 GA48 GA67 GA68 GJ7 GJ8 GJ27 GJ28 GJ47 GJ48 GJ67 GJ68 GK7 GK8 GK27 GK28 GK47 GK48 GK67 GK68 GT7 GT8 GT27 GT28 GT47 GT48 GT67 GT68 GU7 GU8 GU27 GU28 GU47 GU48 GU67 GU68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Ｓ,Ａ,Ｂ,Ｃ,Ｄ,Ｅ,Ｆ,Ｇ,Ｘ"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="H80 R80 AB80 AL80 AV80 BF80 BP80 BZ80 CJ80 CT80 DD80 DN80 DX80 EH80 ER80 FB80 FL80 FV80 GF80 GP80 GZ80 H20 R20 AB20 AL20 AV20 BF20 BP20 BZ20 CJ20 CT20 DD20 DN20 DX20 EH20 ER20 FB20 FL20 FV20 GF20 GP20 GZ20 H40 R40 AB40 AL40 AV40 BF40 BP40 BZ40 CJ40 CT40 DD40 DN40 DX40 EH40 ER40 FB40 FL40 FV40 GF40 GP40 GZ40 H60 R60 AB60 AL60 AV60 BF60 BP60 BZ60 CJ60 CT60 DD60 DN60 DX60 EH60 ER60 FB60 FL60 FV60 GF60 GP60 GZ60" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="H20 H40 H60 H80 R20 R40 R60 R80 AB20 AB40 AB60 AB80 AL20 AL40 AL60 AL80 AV20 AV40 AV60 AV80 BF20 BF40 BF60 BF80 BP20 BP40 BP60 BP80 BZ20 BZ40 BZ60 BZ80 CJ20 CJ40 CJ60 CJ80 CT20 CT40 CT60 CT80 DD20 DD40 DD60 DD80 DN20 DN40 DN60 DN80 DX20 DX40 DX60 DX80 EH20 EH40 EH60 EH80 ER20 ER40 ER60 ER80 FB20 FB40 FB60 FB80 FL20 FL40 FL60 FL80 FV20 FV40 FV60 FV80 GF20 GF40 GF60 GF80 GP20 GP40 GP60 GP80 GZ20 GZ40 GZ60 GZ80" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"＋,－,±"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B34 C34 B35 C35 L34 M34 L35 M35 V34 W34 V35 W35 AF34 AG34 AF35 AG35 AP34 AQ34 AP35 AQ35 AZ34 BA34 AZ35 BA35 BJ34 BK34 BJ35 BK35 BT34 BU34 BT35 BU35 CD34 CE34 CD35 CE35 CN34 CO34 CN35 CO35 CX34 CY34 CX35 CY35 DH34 DI34 DH35 DI35 DR34 DS34 DR35 DS35 EB34 EC34 EB35 EC35 EL34 EM34 EL35 EM35 EV34 EW34 EV35 EW35 FF34 FG34 FF35 FG35 FP34 FQ34 FP35 FQ35 FZ34 GA34 FZ35 GA35 GJ34 GK34 GJ35 GK35 GT34 GU34 GT35 GU35 B74 C74 B75 C75 L74 M74 L75 M75 V74 W74 V75 W75 AF74 AG74 AF75 AG75 AP74 AQ74 AP75 AQ75 AZ74 BA74 AZ75 BA75 BJ74 BK74 BJ75 BK75 BT74 BU74 BT75 BU75 CD74 CE74 CD75 CE75 CN74 CO74 CN75 CO75 CX74 CY74 CX75 CY75 DH74 DI74 DH75 DI75 DR74 DS74 DR75 DS75 EB74 EC74 EB75 EC75 EL74 EM74 EL75 EM75 EV74 EW74 EV75 EW75 FF74 FG74 FF75 FG75 FP74 FQ74 FP75 FQ75 FZ74 GA74 FZ75 GA75 GJ74 GK74 GJ75 GK75 GT74 GU74 GT75 GU75 B54 C54 B55 C55 L54 M54 L55 M55 V54 W54 V55 W55 AF54 AG54 AF55 AG55 AP54 AQ54 AP55 AQ55 AZ54 BA54 AZ55 BA55 BJ54 BK54 BJ55 BK55 BT54 BU54 BT55 BU55 CD54 CE54 CD55 CE55 CN54 CO54 CN55 CO55 CX54 CY54 CX55 CY55 DH54 DI54 DH55 DI55 DR54 DS54 DR55 DS55 EB54 EC54 EB55 EC55 EL54 EM54 EL55 EM55 EV54 EW54 EV55 EW55 FF54 FG54 FF55 FG55 FP54 FQ54 FP55 FQ55 FZ54 GA54 FZ55 GA55 GJ54 GK54 GJ55 GK55 GT54 GU54 GT55 GU55 B14 C14 B15 C15 L14 M14 L15 M15 V14 W14 V15 W15 AF14 AG14 AF15 AG15 AP14 AQ14 AP15 AQ15 AZ14 BA14 AZ15 BA15 BJ14 BK14 BJ15 BK15 BT14 BU14 BT15 BU15 CD14 CE14 CD15 CE15 CN14 CO14 CN15 CO15 CX14 CY14 CX15 CY15 DH14 DI14 DH15 DI15 DR14 DS14 DR15 DS15 EB14 EC14 EB15 EC15 EL14 EM14 EL15 EM15 EV14 EW14 EV15 EW15 FF14 FG14 FF15 FG15 FP14 FQ14 FP15 FQ15 FZ14 GA14 FZ15 GA15 GJ14 GK14 GJ15 GK15 GT14 GU14 GT15 GU15" showDropDown="0" allowBlank="1">
+    <dataValidation sqref="B14 B15 B34 B35 B54 B55 B74 B75 C14 C15 C34 C35 C54 C55 C74 C75 L14 L15 L34 L35 L54 L55 L74 L75 M14 M15 M34 M35 M54 M55 M74 M75 V14 V15 V34 V35 V54 V55 V74 V75 W14 W15 W34 W35 W54 W55 W74 W75 AF14 AF15 AF34 AF35 AF54 AF55 AF74 AF75 AG14 AG15 AG34 AG35 AG54 AG55 AG74 AG75 AP14 AP15 AP34 AP35 AP54 AP55 AP74 AP75 AQ14 AQ15 AQ34 AQ35 AQ54 AQ55 AQ74 AQ75 AZ14 AZ15 AZ34 AZ35 AZ54 AZ55 AZ74 AZ75 BA14 BA15 BA34 BA35 BA54 BA55 BA74 BA75 BJ14 BJ15 BJ34 BJ35 BJ54 BJ55 BJ74 BJ75 BK14 BK15 BK34 BK35 BK54 BK55 BK74 BK75 BT14 BT15 BT34 BT35 BT54 BT55 BT74 BT75 BU14 BU15 BU34 BU35 BU54 BU55 BU74 BU75 CD14 CD15 CD34 CD35 CD54 CD55 CD74 CD75 CE14 CE15 CE34 CE35 CE54 CE55 CE74 CE75 CN14 CN15 CN34 CN35 CN54 CN55 CN74 CN75 CO14 CO15 CO34 CO35 CO54 CO55 CO74 CO75 CX14 CX15 CX34 CX35 CX54 CX55 CX74 CX75 CY14 CY15 CY34 CY35 CY54 CY55 CY74 CY75 DH14 DH15 DH34 DH35 DH54 DH55 DH74 DH75 DI14 DI15 DI34 DI35 DI54 DI55 DI74 DI75 DR14 DR15 DR34 DR35 DR54 DR55 DR74 DR75 DS14 DS15 DS34 DS35 DS54 DS55 DS74 DS75 EB14 EB15 EB34 EB35 EB54 EB55 EB74 EB75 EC14 EC15 EC34 EC35 EC54 EC55 EC74 EC75 EL14 EL15 EL34 EL35 EL54 EL55 EL74 EL75 EM14 EM15 EM34 EM35 EM54 EM55 EM74 EM75 EV14 EV15 EV34 EV35 EV54 EV55 EV74 EV75 EW14 EW15 EW34 EW35 EW54 EW55 EW74 EW75 FF14 FF15 FF34 FF35 FF54 FF55 FF74 FF75 FG14 FG15 FG34 FG35 FG54 FG55 FG74 FG75 FP14 FP15 FP34 FP35 FP54 FP55 FP74 FP75 FQ14 FQ15 FQ34 FQ35 FQ54 FQ55 FQ74 FQ75 FZ14 FZ15 FZ34 FZ35 FZ54 FZ55 FZ74 FZ75 GA14 GA15 GA34 GA35 GA54 GA55 GA74 GA75 GJ14 GJ15 GJ34 GJ35 GJ54 GJ55 GJ74 GJ75 GK14 GK15 GK34 GK35 GK54 GK55 GK74 GK75 GT14 GT15 GT34 GT35 GT54 GT55 GT74 GT75 GU14 GU15 GU34 GU35 GU54 GU55 GU74 GU75" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"塾長,文章,金城,鈴木,石川,高山,佐藤,金子,吉田,工藤,真下,岩本,染谷"</formula1>
     </dataValidation>
   </dataValidations>
